--- a/research/traditional_assets/database/data/india/india_utility_water.xlsx
+++ b/research/traditional_assets/database/data/india/india_utility_water.xlsx
@@ -1139,7 +1139,7 @@
         <v>1.06680584551148</v>
       </c>
       <c r="H2">
-        <v>3.89906054279749</v>
+        <v>3.8990605427975</v>
       </c>
       <c r="I2">
         <v>0.0410408802505823</v>
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07663207243653683</v>
+        <v>0.0764336762192272</v>
       </c>
       <c r="C2">
-        <v>1243.384591192226</v>
+        <v>1238.494051300919</v>
       </c>
       <c r="D2">
-        <v>1167.384591192226</v>
+        <v>1174.945051300919</v>
       </c>
       <c r="E2">
-        <v>-51.1</v>
+        <v>-38.649</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>12.451</v>
       </c>
       <c r="G2">
         <v>76</v>
@@ -1451,28 +1451,28 @@
         <v>46.969</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.6262852999999999</v>
       </c>
       <c r="N2">
-        <v>46.969</v>
+        <v>46.3427147</v>
       </c>
       <c r="O2">
-        <v>14.0907</v>
+        <v>13.90281441</v>
       </c>
       <c r="P2">
-        <v>32.8783</v>
+        <v>32.43990029</v>
       </c>
       <c r="Q2">
-        <v>33.8093</v>
+        <v>33.37090029</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07663207243653683</v>
+        <v>0.07685007698911839</v>
       </c>
       <c r="T2">
-        <v>0.4244150824346248</v>
+        <v>0.42741599715891</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>74.99617187246771</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.0764336762192272</v>
+        <v>0.07623528000191761</v>
       </c>
       <c r="C3">
-        <v>1238.494051300919</v>
+        <v>1233.702079038139</v>
       </c>
       <c r="D3">
-        <v>1174.945051300919</v>
+        <v>1182.604079038139</v>
       </c>
       <c r="E3">
-        <v>-38.649</v>
+        <v>-26.198</v>
       </c>
       <c r="F3">
-        <v>12.451</v>
+        <v>24.902</v>
       </c>
       <c r="G3">
         <v>76</v>
@@ -1533,28 +1533,28 @@
         <v>46.969</v>
       </c>
       <c r="M3">
-        <v>0.6262852999999999</v>
+        <v>1.2525706</v>
       </c>
       <c r="N3">
-        <v>46.3427147</v>
+        <v>45.7164294</v>
       </c>
       <c r="O3">
-        <v>13.90281441</v>
+        <v>13.71492882</v>
       </c>
       <c r="P3">
-        <v>32.43990029</v>
+        <v>32.00150058</v>
       </c>
       <c r="Q3">
-        <v>33.37090029</v>
+        <v>32.93250058</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07685007698911839</v>
+        <v>0.07707253061420163</v>
       </c>
       <c r="T3">
-        <v>0.42741599715891</v>
+        <v>0.4304781550408337</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>74.99617187246771</v>
+        <v>37.49808593623386</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07623528000191761</v>
+        <v>0.07603688378460798</v>
       </c>
       <c r="C4">
-        <v>1233.702079038139</v>
+        <v>1229.010614628097</v>
       </c>
       <c r="D4">
-        <v>1182.604079038139</v>
+        <v>1190.363614628097</v>
       </c>
       <c r="E4">
-        <v>-26.198</v>
+        <v>-13.74700000000001</v>
       </c>
       <c r="F4">
-        <v>24.902</v>
+        <v>37.35299999999999</v>
       </c>
       <c r="G4">
         <v>76</v>
@@ -1615,28 +1615,28 @@
         <v>46.969</v>
       </c>
       <c r="M4">
-        <v>1.2525706</v>
+        <v>1.8788559</v>
       </c>
       <c r="N4">
-        <v>45.7164294</v>
+        <v>45.0901441</v>
       </c>
       <c r="O4">
-        <v>13.71492882</v>
+        <v>13.52704323</v>
       </c>
       <c r="P4">
-        <v>32.00150058</v>
+        <v>31.56310087</v>
       </c>
       <c r="Q4">
-        <v>32.93250058</v>
+        <v>32.49410087</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07707253061420163</v>
+        <v>0.07729957091196699</v>
       </c>
       <c r="T4">
-        <v>0.4304781550408337</v>
+        <v>0.4336034501986733</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>37.49808593623386</v>
+        <v>24.99872395748924</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07603688378460798</v>
+        <v>0.07583848756729837</v>
       </c>
       <c r="C5">
-        <v>1229.010614628097</v>
+        <v>1224.421649553661</v>
       </c>
       <c r="D5">
-        <v>1190.363614628097</v>
+        <v>1198.225649553661</v>
       </c>
       <c r="E5">
-        <v>-13.74700000000001</v>
+        <v>-1.296000000000006</v>
       </c>
       <c r="F5">
-        <v>37.35299999999999</v>
+        <v>49.80399999999999</v>
       </c>
       <c r="G5">
         <v>76</v>
@@ -1697,28 +1697,28 @@
         <v>46.969</v>
       </c>
       <c r="M5">
-        <v>1.8788559</v>
+        <v>2.5051412</v>
       </c>
       <c r="N5">
-        <v>45.0901441</v>
+        <v>44.4638588</v>
       </c>
       <c r="O5">
-        <v>13.52704323</v>
+        <v>13.33915764</v>
       </c>
       <c r="P5">
-        <v>31.56310087</v>
+        <v>31.12470116</v>
       </c>
       <c r="Q5">
-        <v>32.49410087</v>
+        <v>32.05570116</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07729957091196699</v>
+        <v>0.0775313412159358</v>
       </c>
       <c r="T5">
-        <v>0.4336034501986733</v>
+        <v>0.4367938556723013</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>24.99872395748924</v>
+        <v>18.74904296811693</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07583848756729837</v>
+        <v>0.07564009134998877</v>
       </c>
       <c r="C6">
-        <v>1224.421649553661</v>
+        <v>1219.93722826036</v>
       </c>
       <c r="D6">
-        <v>1198.225649553661</v>
+        <v>1206.19222826036</v>
       </c>
       <c r="E6">
-        <v>-1.296000000000006</v>
+        <v>11.15499999999999</v>
       </c>
       <c r="F6">
-        <v>49.80399999999999</v>
+        <v>62.255</v>
       </c>
       <c r="G6">
         <v>76</v>
@@ -1779,28 +1779,28 @@
         <v>46.969</v>
       </c>
       <c r="M6">
-        <v>2.5051412</v>
+        <v>3.131426499999999</v>
       </c>
       <c r="N6">
-        <v>44.4638588</v>
+        <v>43.8375735</v>
       </c>
       <c r="O6">
-        <v>13.33915764</v>
+        <v>13.15127205</v>
       </c>
       <c r="P6">
-        <v>31.12470116</v>
+        <v>30.68630145</v>
       </c>
       <c r="Q6">
-        <v>32.05570116</v>
+        <v>31.61730145</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.0775313412159358</v>
+        <v>0.07776799089472503</v>
       </c>
       <c r="T6">
-        <v>0.4367938556723013</v>
+        <v>0.440051427576953</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>18.74904296811693</v>
+        <v>14.99923437449355</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07564009134998877</v>
+        <v>0.07550469513267916</v>
       </c>
       <c r="C7">
-        <v>1219.93722826036</v>
+        <v>1212.984142456256</v>
       </c>
       <c r="D7">
-        <v>1206.19222826036</v>
+        <v>1211.690142456256</v>
       </c>
       <c r="E7">
-        <v>11.15499999999999</v>
+        <v>23.606</v>
       </c>
       <c r="F7">
-        <v>62.255</v>
+        <v>74.706</v>
       </c>
       <c r="G7">
         <v>76</v>
@@ -1861,45 +1861,45 @@
         <v>46.969</v>
       </c>
       <c r="M7">
-        <v>3.131426499999999</v>
+        <v>3.8697708</v>
       </c>
       <c r="N7">
-        <v>43.8375735</v>
+        <v>43.0992292</v>
       </c>
       <c r="O7">
-        <v>13.15127205</v>
+        <v>12.92976876</v>
       </c>
       <c r="P7">
-        <v>30.68630145</v>
+        <v>30.16946044</v>
       </c>
       <c r="Q7">
-        <v>31.61730145</v>
+        <v>31.10046044</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07776799089472503</v>
+        <v>0.07800967567306294</v>
       </c>
       <c r="T7">
-        <v>0.440051427576953</v>
+        <v>0.4433783095221293</v>
       </c>
       <c r="U7">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V7">
         <v>0.3</v>
       </c>
       <c r="W7">
-        <v>0.03521</v>
+        <v>0.03625999999999999</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y7">
-        <v>14.99923437449355</v>
+        <v>12.13741134229448</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07550469513267916</v>
+        <v>0.07531679891536956</v>
       </c>
       <c r="C8">
-        <v>1212.984142456256</v>
+        <v>1208.246444802206</v>
       </c>
       <c r="D8">
-        <v>1211.690142456256</v>
+        <v>1219.403444802206</v>
       </c>
       <c r="E8">
-        <v>23.60599999999999</v>
+        <v>36.05699999999998</v>
       </c>
       <c r="F8">
-        <v>74.70599999999999</v>
+        <v>87.15699999999998</v>
       </c>
       <c r="G8">
         <v>76</v>
@@ -1943,28 +1943,28 @@
         <v>46.969</v>
       </c>
       <c r="M8">
-        <v>3.8697708</v>
+        <v>4.514732599999999</v>
       </c>
       <c r="N8">
-        <v>43.0992292</v>
+        <v>42.45426740000001</v>
       </c>
       <c r="O8">
-        <v>12.92976876</v>
+        <v>12.73628022</v>
       </c>
       <c r="P8">
-        <v>30.16946044</v>
+        <v>29.71798718000001</v>
       </c>
       <c r="Q8">
-        <v>31.10046044</v>
+        <v>30.64898718000001</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07800967567306294</v>
+        <v>0.07825655797351565</v>
       </c>
       <c r="T8">
-        <v>0.4433783095221293</v>
+        <v>0.4467767373155889</v>
       </c>
       <c r="U8">
         <v>0.0518</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>12.13741134229449</v>
+        <v>10.40349543625242</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07531679891536955</v>
+        <v>0.07522410269805994</v>
       </c>
       <c r="C9">
-        <v>1208.246444802206</v>
+        <v>1199.636992252859</v>
       </c>
       <c r="D9">
-        <v>1219.403444802206</v>
+        <v>1223.244992252859</v>
       </c>
       <c r="E9">
-        <v>36.057</v>
+        <v>48.50799999999999</v>
       </c>
       <c r="F9">
-        <v>87.157</v>
+        <v>99.60799999999999</v>
       </c>
       <c r="G9">
         <v>76</v>
@@ -2025,45 +2025,45 @@
         <v>46.969</v>
       </c>
       <c r="M9">
-        <v>4.514732599999999</v>
+        <v>5.329027999999999</v>
       </c>
       <c r="N9">
-        <v>42.4542674</v>
+        <v>41.639972</v>
       </c>
       <c r="O9">
-        <v>12.73628022</v>
+        <v>12.4919916</v>
       </c>
       <c r="P9">
-        <v>29.71798718</v>
+        <v>29.1479804</v>
       </c>
       <c r="Q9">
-        <v>30.64898718</v>
+        <v>30.0789804</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07825655797351565</v>
+        <v>0.07850880728049994</v>
       </c>
       <c r="T9">
-        <v>0.4467767373155889</v>
+        <v>0.4502490439741237</v>
       </c>
       <c r="U9">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V9">
         <v>0.3</v>
       </c>
       <c r="W9">
-        <v>0.03625999999999999</v>
+        <v>0.03745</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y9">
-        <v>10.40349543625242</v>
+        <v>8.813802442021323</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07522410269805994</v>
+        <v>0.07504810648075033</v>
       </c>
       <c r="C10">
-        <v>1199.636992252859</v>
+        <v>1194.546690683751</v>
       </c>
       <c r="D10">
-        <v>1223.244992252859</v>
+        <v>1230.605690683751</v>
       </c>
       <c r="E10">
-        <v>48.50799999999999</v>
+        <v>60.95899999999998</v>
       </c>
       <c r="F10">
-        <v>99.60799999999999</v>
+        <v>112.059</v>
       </c>
       <c r="G10">
         <v>76</v>
@@ -2107,28 +2107,28 @@
         <v>46.969</v>
       </c>
       <c r="M10">
-        <v>5.329027999999999</v>
+        <v>5.995156499999999</v>
       </c>
       <c r="N10">
-        <v>41.639972</v>
+        <v>40.9738435</v>
       </c>
       <c r="O10">
-        <v>12.4919916</v>
+        <v>12.29215305</v>
       </c>
       <c r="P10">
-        <v>29.1479804</v>
+        <v>28.68169045</v>
       </c>
       <c r="Q10">
-        <v>30.0789804</v>
+        <v>29.61269045</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07850880728049994</v>
+        <v>0.07876660052829706</v>
       </c>
       <c r="T10">
-        <v>0.4502490439741237</v>
+        <v>0.4537976650647142</v>
       </c>
       <c r="U10">
         <v>0.0535</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>8.813802442021323</v>
+        <v>7.834491059574509</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07504810648075033</v>
+        <v>0.07492811026344072</v>
       </c>
       <c r="C11">
-        <v>1194.546690683751</v>
+        <v>1187.165296179823</v>
       </c>
       <c r="D11">
-        <v>1230.605690683751</v>
+        <v>1235.675296179823</v>
       </c>
       <c r="E11">
-        <v>60.95899999999998</v>
+        <v>73.40999999999997</v>
       </c>
       <c r="F11">
-        <v>112.059</v>
+        <v>124.51</v>
       </c>
       <c r="G11">
         <v>76</v>
@@ -2189,45 +2189,45 @@
         <v>46.969</v>
       </c>
       <c r="M11">
-        <v>5.995156499999999</v>
+        <v>6.760892999999998</v>
       </c>
       <c r="N11">
-        <v>40.9738435</v>
+        <v>40.20810700000001</v>
       </c>
       <c r="O11">
-        <v>12.29215305</v>
+        <v>12.0624321</v>
       </c>
       <c r="P11">
-        <v>28.68169045</v>
+        <v>28.1456749</v>
       </c>
       <c r="Q11">
-        <v>29.61269045</v>
+        <v>29.0766749</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07876660052829706</v>
+        <v>0.07903012251493413</v>
       </c>
       <c r="T11">
-        <v>0.4537976650647142</v>
+        <v>0.4574251444017622</v>
       </c>
       <c r="U11">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V11">
         <v>0.3</v>
       </c>
       <c r="W11">
-        <v>0.03745</v>
+        <v>0.03801</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y11">
-        <v>7.834491059574509</v>
+        <v>6.947159199235961</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07492811026344072</v>
+        <v>0.0747577140461311</v>
       </c>
       <c r="C12">
-        <v>1187.165296179823</v>
+        <v>1181.985394856899</v>
       </c>
       <c r="D12">
-        <v>1235.675296179823</v>
+        <v>1242.946394856899</v>
       </c>
       <c r="E12">
-        <v>73.41</v>
+        <v>85.86099999999999</v>
       </c>
       <c r="F12">
-        <v>124.51</v>
+        <v>136.961</v>
       </c>
       <c r="G12">
         <v>76</v>
@@ -2271,28 +2271,28 @@
         <v>46.969</v>
       </c>
       <c r="M12">
-        <v>6.760892999999999</v>
+        <v>7.436982299999999</v>
       </c>
       <c r="N12">
-        <v>40.208107</v>
+        <v>39.5320177</v>
       </c>
       <c r="O12">
-        <v>12.0624321</v>
+        <v>11.85960531</v>
       </c>
       <c r="P12">
-        <v>28.1456749</v>
+        <v>27.67241239000001</v>
       </c>
       <c r="Q12">
-        <v>29.0766749</v>
+        <v>28.60341239000001</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07903012251493413</v>
+        <v>0.07929956634396754</v>
       </c>
       <c r="T12">
-        <v>0.4574251444017622</v>
+        <v>0.4611341401284069</v>
       </c>
       <c r="U12">
         <v>0.0543</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>6.947159199235959</v>
+        <v>6.315599272032691</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.0747577140461311</v>
+        <v>0.0746713178288215</v>
       </c>
       <c r="C13">
-        <v>1181.985394856899</v>
+        <v>1173.253860226334</v>
       </c>
       <c r="D13">
-        <v>1242.946394856899</v>
+        <v>1246.665860226334</v>
       </c>
       <c r="E13">
-        <v>85.86099999999999</v>
+        <v>98.31199999999998</v>
       </c>
       <c r="F13">
-        <v>136.961</v>
+        <v>149.412</v>
       </c>
       <c r="G13">
         <v>76</v>
@@ -2353,45 +2353,45 @@
         <v>46.969</v>
       </c>
       <c r="M13">
-        <v>7.436982299999999</v>
+        <v>8.262483599999999</v>
       </c>
       <c r="N13">
-        <v>39.5320177</v>
+        <v>38.7065164</v>
       </c>
       <c r="O13">
-        <v>11.85960531</v>
+        <v>11.61195492</v>
       </c>
       <c r="P13">
-        <v>27.67241239000001</v>
+        <v>27.09456148</v>
       </c>
       <c r="Q13">
-        <v>28.60341239000001</v>
+        <v>28.02556148</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07929956634396754</v>
+        <v>0.07957513389638807</v>
       </c>
       <c r="T13">
-        <v>0.4611341401284069</v>
+        <v>0.4649274312124753</v>
       </c>
       <c r="U13">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V13">
         <v>0.3</v>
       </c>
       <c r="W13">
-        <v>0.03801</v>
+        <v>0.03871</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y13">
-        <v>6.315599272032691</v>
+        <v>5.684610375505011</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.0746713178288215</v>
+        <v>0.07450792161151189</v>
       </c>
       <c r="C14">
-        <v>1173.253860226334</v>
+        <v>1167.898479636425</v>
       </c>
       <c r="D14">
-        <v>1246.665860226334</v>
+        <v>1253.761479636425</v>
       </c>
       <c r="E14">
-        <v>98.31199999999998</v>
+        <v>110.763</v>
       </c>
       <c r="F14">
-        <v>149.412</v>
+        <v>161.863</v>
       </c>
       <c r="G14">
         <v>76</v>
@@ -2435,28 +2435,28 @@
         <v>46.969</v>
       </c>
       <c r="M14">
-        <v>8.262483599999999</v>
+        <v>8.951023900000001</v>
       </c>
       <c r="N14">
-        <v>38.7065164</v>
+        <v>38.0179761</v>
       </c>
       <c r="O14">
-        <v>11.61195492</v>
+        <v>11.40539283</v>
       </c>
       <c r="P14">
-        <v>27.09456148</v>
+        <v>26.61258327</v>
       </c>
       <c r="Q14">
-        <v>28.02556148</v>
+        <v>27.54358327</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07957513389638807</v>
+        <v>0.07985703633507113</v>
       </c>
       <c r="T14">
-        <v>0.4649274312124753</v>
+        <v>0.4688079243904303</v>
       </c>
       <c r="U14">
         <v>0.0553</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>5.684610375505011</v>
+        <v>5.247332654312318</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07450792161151189</v>
+        <v>0.07434452539420228</v>
       </c>
       <c r="C15">
-        <v>1167.898479636425</v>
+        <v>1162.624333353625</v>
       </c>
       <c r="D15">
-        <v>1253.761479636425</v>
+        <v>1260.938333353625</v>
       </c>
       <c r="E15">
-        <v>110.763</v>
+        <v>123.214</v>
       </c>
       <c r="F15">
-        <v>161.863</v>
+        <v>174.314</v>
       </c>
       <c r="G15">
         <v>76</v>
@@ -2517,28 +2517,28 @@
         <v>46.969</v>
       </c>
       <c r="M15">
-        <v>8.951023900000001</v>
+        <v>9.639564200000001</v>
       </c>
       <c r="N15">
-        <v>38.0179761</v>
+        <v>37.3294358</v>
       </c>
       <c r="O15">
-        <v>11.40539283</v>
+        <v>11.19883074</v>
       </c>
       <c r="P15">
-        <v>26.61258327</v>
+        <v>26.13060506</v>
       </c>
       <c r="Q15">
-        <v>27.54358327</v>
+        <v>27.06160506</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07985703633507113</v>
+        <v>0.08014549464442125</v>
       </c>
       <c r="T15">
-        <v>0.4688079243904303</v>
+        <v>0.4727786615957797</v>
       </c>
       <c r="U15">
         <v>0.0553</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>5.247332654312318</v>
+        <v>4.872523179004295</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07434452539420228</v>
+        <v>0.07418112917689267</v>
       </c>
       <c r="C16">
-        <v>1162.624333353625</v>
+        <v>1157.432824427659</v>
       </c>
       <c r="D16">
-        <v>1260.938333353625</v>
+        <v>1268.197824427659</v>
       </c>
       <c r="E16">
-        <v>123.214</v>
+        <v>135.665</v>
       </c>
       <c r="F16">
-        <v>174.314</v>
+        <v>186.765</v>
       </c>
       <c r="G16">
         <v>76</v>
@@ -2599,28 +2599,28 @@
         <v>46.969</v>
       </c>
       <c r="M16">
-        <v>9.639564200000001</v>
+        <v>10.3281045</v>
       </c>
       <c r="N16">
-        <v>37.3294358</v>
+        <v>36.6408955</v>
       </c>
       <c r="O16">
-        <v>11.19883074</v>
+        <v>10.99226865</v>
       </c>
       <c r="P16">
-        <v>26.13060506</v>
+        <v>25.64862685</v>
       </c>
       <c r="Q16">
-        <v>27.06160506</v>
+        <v>26.57962685</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08014549464442125</v>
+        <v>0.08044074020810901</v>
       </c>
       <c r="T16">
-        <v>0.4727786615957797</v>
+        <v>0.4768428279118431</v>
       </c>
       <c r="U16">
         <v>0.0553</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>4.872523179004295</v>
+        <v>4.547688300404008</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07418112917689267</v>
+        <v>0.07429773295958304</v>
       </c>
       <c r="C17">
-        <v>1157.432824427659</v>
+        <v>1139.792756801203</v>
       </c>
       <c r="D17">
-        <v>1268.197824427659</v>
+        <v>1263.008756801203</v>
       </c>
       <c r="E17">
-        <v>135.665</v>
+        <v>148.116</v>
       </c>
       <c r="F17">
-        <v>186.765</v>
+        <v>199.216</v>
       </c>
       <c r="G17">
         <v>76</v>
@@ -2681,45 +2681,45 @@
         <v>46.969</v>
       </c>
       <c r="M17">
-        <v>10.3281045</v>
+        <v>11.5146848</v>
       </c>
       <c r="N17">
-        <v>36.6408955</v>
+        <v>35.4543152</v>
       </c>
       <c r="O17">
-        <v>10.99226865</v>
+        <v>10.63629456</v>
       </c>
       <c r="P17">
-        <v>25.64862685</v>
+        <v>24.81802064</v>
       </c>
       <c r="Q17">
-        <v>26.57962685</v>
+        <v>25.74902064</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08044074020810901</v>
+        <v>0.08074301542807506</v>
       </c>
       <c r="T17">
-        <v>0.4768428279118431</v>
+        <v>0.4810037600925747</v>
       </c>
       <c r="U17">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V17">
         <v>0.3</v>
       </c>
       <c r="W17">
-        <v>0.03871</v>
+        <v>0.04046</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y17">
-        <v>4.547688300404009</v>
+        <v>4.079052168236512</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07429773295958304</v>
+        <v>0.07456833674227344</v>
       </c>
       <c r="C18">
-        <v>1139.792756801203</v>
+        <v>1115.461509770471</v>
       </c>
       <c r="D18">
-        <v>1263.008756801203</v>
+        <v>1251.128509770471</v>
       </c>
       <c r="E18">
-        <v>148.116</v>
+        <v>160.567</v>
       </c>
       <c r="F18">
-        <v>199.216</v>
+        <v>211.667</v>
       </c>
       <c r="G18">
         <v>76</v>
@@ -2763,45 +2763,45 @@
         <v>46.969</v>
       </c>
       <c r="M18">
-        <v>11.5146848</v>
+        <v>12.9751871</v>
       </c>
       <c r="N18">
-        <v>35.4543152</v>
+        <v>33.9938129</v>
       </c>
       <c r="O18">
-        <v>10.63629456</v>
+        <v>10.19814387</v>
       </c>
       <c r="P18">
-        <v>24.81802064</v>
+        <v>23.79566903</v>
       </c>
       <c r="Q18">
-        <v>25.74902064</v>
+        <v>24.72666903</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08074301542807506</v>
+        <v>0.08105257438828126</v>
       </c>
       <c r="T18">
-        <v>0.4810037600925747</v>
+        <v>0.4852649556993481</v>
       </c>
       <c r="U18">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V18">
         <v>0.3</v>
       </c>
       <c r="W18">
-        <v>0.04046</v>
+        <v>0.04291</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y18">
-        <v>4.079052168236512</v>
+        <v>3.61990926512343</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07456833674227344</v>
+        <v>0.07479974052496383</v>
       </c>
       <c r="C19">
-        <v>1115.461509770471</v>
+        <v>1093.027114589971</v>
       </c>
       <c r="D19">
-        <v>1251.128509770471</v>
+        <v>1241.145114589971</v>
       </c>
       <c r="E19">
-        <v>160.567</v>
+        <v>173.018</v>
       </c>
       <c r="F19">
-        <v>211.667</v>
+        <v>224.118</v>
       </c>
       <c r="G19">
         <v>76</v>
@@ -2845,45 +2845,45 @@
         <v>46.969</v>
       </c>
       <c r="M19">
-        <v>12.9751871</v>
+        <v>14.3659638</v>
       </c>
       <c r="N19">
-        <v>33.9938129</v>
+        <v>32.6030362</v>
       </c>
       <c r="O19">
-        <v>10.19814387</v>
+        <v>9.780910859999999</v>
       </c>
       <c r="P19">
-        <v>23.79566903</v>
+        <v>22.82212534</v>
       </c>
       <c r="Q19">
-        <v>24.72666903</v>
+        <v>23.75312534</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08105257438828126</v>
+        <v>0.08136968356702906</v>
       </c>
       <c r="T19">
-        <v>0.4852649556993481</v>
+        <v>0.4896300829062866</v>
       </c>
       <c r="U19">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V19">
         <v>0.3</v>
       </c>
       <c r="W19">
-        <v>0.04291</v>
+        <v>0.04487</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y19">
-        <v>3.61990926512343</v>
+        <v>3.26946389771635</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07479974052496384</v>
+        <v>0.07469794430765422</v>
       </c>
       <c r="C20">
-        <v>1093.02711458997</v>
+        <v>1084.948186058186</v>
       </c>
       <c r="D20">
-        <v>1241.14511458997</v>
+        <v>1245.517186058186</v>
       </c>
       <c r="E20">
-        <v>173.018</v>
+        <v>185.469</v>
       </c>
       <c r="F20">
-        <v>224.118</v>
+        <v>236.569</v>
       </c>
       <c r="G20">
         <v>76</v>
@@ -2927,28 +2927,28 @@
         <v>46.969</v>
       </c>
       <c r="M20">
-        <v>14.3659638</v>
+        <v>15.1640729</v>
       </c>
       <c r="N20">
-        <v>32.60303620000001</v>
+        <v>31.8049271</v>
       </c>
       <c r="O20">
-        <v>9.780910860000001</v>
+        <v>9.54147813</v>
       </c>
       <c r="P20">
-        <v>22.82212534000001</v>
+        <v>22.26344897</v>
       </c>
       <c r="Q20">
-        <v>23.75312534000001</v>
+        <v>23.19444897</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08136968356702906</v>
+        <v>0.08169462260204224</v>
       </c>
       <c r="T20">
-        <v>0.4896300829062866</v>
+        <v>0.494102991031915</v>
       </c>
       <c r="U20">
         <v>0.0641</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>3.269463897716351</v>
+        <v>3.097386850468122</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07469794430765422</v>
+        <v>0.07568814809034462</v>
       </c>
       <c r="C21">
-        <v>1084.948186058186</v>
+        <v>1031.232808442259</v>
       </c>
       <c r="D21">
-        <v>1245.517186058186</v>
+        <v>1204.252808442259</v>
       </c>
       <c r="E21">
-        <v>185.469</v>
+        <v>197.92</v>
       </c>
       <c r="F21">
-        <v>236.569</v>
+        <v>249.02</v>
       </c>
       <c r="G21">
         <v>76</v>
@@ -3009,45 +3009,45 @@
         <v>46.969</v>
       </c>
       <c r="M21">
-        <v>15.1640729</v>
+        <v>17.904538</v>
       </c>
       <c r="N21">
-        <v>31.8049271</v>
+        <v>29.064462</v>
       </c>
       <c r="O21">
-        <v>9.54147813</v>
+        <v>8.7193386</v>
       </c>
       <c r="P21">
-        <v>22.26344897</v>
+        <v>20.3451234</v>
       </c>
       <c r="Q21">
-        <v>23.19444897</v>
+        <v>21.2761234</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08169462260204224</v>
+        <v>0.08202768511293076</v>
       </c>
       <c r="T21">
-        <v>0.494102991031915</v>
+        <v>0.4986877218606841</v>
       </c>
       <c r="U21">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V21">
         <v>0.3</v>
       </c>
       <c r="W21">
-        <v>0.04487</v>
+        <v>0.05033</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y21">
-        <v>3.097386850468122</v>
+        <v>2.623301422242786</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07568814809034462</v>
+        <v>0.076214251873035</v>
       </c>
       <c r="C22">
-        <v>1031.232808442259</v>
+        <v>997.9507204220176</v>
       </c>
       <c r="D22">
-        <v>1204.252808442259</v>
+        <v>1183.421720422018</v>
       </c>
       <c r="E22">
-        <v>197.92</v>
+        <v>210.371</v>
       </c>
       <c r="F22">
-        <v>249.02</v>
+        <v>261.471</v>
       </c>
       <c r="G22">
         <v>76</v>
@@ -3091,45 +3091,45 @@
         <v>46.969</v>
       </c>
       <c r="M22">
-        <v>17.904538</v>
+        <v>19.8195018</v>
       </c>
       <c r="N22">
-        <v>29.064462</v>
+        <v>27.1494982</v>
       </c>
       <c r="O22">
-        <v>8.7193386</v>
+        <v>8.14484946</v>
       </c>
       <c r="P22">
-        <v>20.3451234</v>
+        <v>19.00464874</v>
       </c>
       <c r="Q22">
-        <v>21.2761234</v>
+        <v>19.93564874</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08202768511293076</v>
+        <v>0.08236917958612025</v>
       </c>
       <c r="T22">
-        <v>0.4986877218606841</v>
+        <v>0.5033885218243588</v>
       </c>
       <c r="U22">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V22">
         <v>0.3</v>
       </c>
       <c r="W22">
-        <v>0.05033</v>
+        <v>0.05306</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y22">
-        <v>2.623301422242786</v>
+        <v>2.369837570791007</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.076214251873035</v>
+        <v>0.07619435565572538</v>
       </c>
       <c r="C23">
-        <v>997.9507204220176</v>
+        <v>986.2743910873587</v>
       </c>
       <c r="D23">
-        <v>1183.421720422018</v>
+        <v>1184.196391087359</v>
       </c>
       <c r="E23">
-        <v>210.371</v>
+        <v>222.822</v>
       </c>
       <c r="F23">
-        <v>261.4709999999999</v>
+        <v>273.922</v>
       </c>
       <c r="G23">
         <v>76</v>
@@ -3173,28 +3173,28 @@
         <v>46.969</v>
       </c>
       <c r="M23">
-        <v>19.8195018</v>
+        <v>20.7632876</v>
       </c>
       <c r="N23">
-        <v>27.1494982</v>
+        <v>26.2057124</v>
       </c>
       <c r="O23">
-        <v>8.144849460000001</v>
+        <v>7.861713720000001</v>
       </c>
       <c r="P23">
-        <v>19.00464874</v>
+        <v>18.34399868</v>
       </c>
       <c r="Q23">
-        <v>19.93564874</v>
+        <v>19.27499868</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08236917958612025</v>
+        <v>0.08271943032785306</v>
       </c>
       <c r="T23">
-        <v>0.5033885218243587</v>
+        <v>0.5082098551204353</v>
       </c>
       <c r="U23">
         <v>0.07580000000000001</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>2.369837570791008</v>
+        <v>2.262117681209598</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07619435565572538</v>
+        <v>0.07617445943841579</v>
       </c>
       <c r="C24">
-        <v>986.2743910873587</v>
+        <v>974.5990766195434</v>
       </c>
       <c r="D24">
-        <v>1184.196391087359</v>
+        <v>1184.972076619543</v>
       </c>
       <c r="E24">
-        <v>222.822</v>
+        <v>235.273</v>
       </c>
       <c r="F24">
-        <v>273.922</v>
+        <v>286.373</v>
       </c>
       <c r="G24">
         <v>76</v>
@@ -3255,28 +3255,28 @@
         <v>46.969</v>
       </c>
       <c r="M24">
-        <v>20.7632876</v>
+        <v>21.7070734</v>
       </c>
       <c r="N24">
-        <v>26.2057124</v>
+        <v>25.2619266</v>
       </c>
       <c r="O24">
-        <v>7.861713720000001</v>
+        <v>7.578577979999999</v>
       </c>
       <c r="P24">
-        <v>18.34399868</v>
+        <v>17.68334862</v>
       </c>
       <c r="Q24">
-        <v>19.27499868</v>
+        <v>18.61434862</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08271943032785306</v>
+        <v>0.08307877849144907</v>
       </c>
       <c r="T24">
-        <v>0.5082098551204353</v>
+        <v>0.5131564178527735</v>
       </c>
       <c r="U24">
         <v>0.07580000000000001</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>2.262117681209598</v>
+        <v>2.163764738548311</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07617445943841579</v>
+        <v>0.07615456322110617</v>
       </c>
       <c r="C25">
-        <v>974.5990766195434</v>
+        <v>962.924779014189</v>
       </c>
       <c r="D25">
-        <v>1184.972076619543</v>
+        <v>1185.748779014189</v>
       </c>
       <c r="E25">
-        <v>235.273</v>
+        <v>247.724</v>
       </c>
       <c r="F25">
-        <v>286.373</v>
+        <v>298.824</v>
       </c>
       <c r="G25">
         <v>76</v>
@@ -3337,28 +3337,28 @@
         <v>46.969</v>
       </c>
       <c r="M25">
-        <v>21.7070734</v>
+        <v>22.6508592</v>
       </c>
       <c r="N25">
-        <v>25.2619266</v>
+        <v>24.3181408</v>
       </c>
       <c r="O25">
-        <v>7.578577979999999</v>
+        <v>7.295442239999999</v>
       </c>
       <c r="P25">
-        <v>17.68334862</v>
+        <v>17.02269856</v>
       </c>
       <c r="Q25">
-        <v>18.61434862</v>
+        <v>17.95369856</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08307877849144907</v>
+        <v>0.083447583185666</v>
       </c>
       <c r="T25">
-        <v>0.5131564178527735</v>
+        <v>0.5182331532885944</v>
       </c>
       <c r="U25">
         <v>0.07580000000000001</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>2.163764738548311</v>
+        <v>2.073607874442131</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07615456322110617</v>
+        <v>0.07861966700379656</v>
       </c>
       <c r="C26">
-        <v>962.9247790141891</v>
+        <v>861.4115164345516</v>
       </c>
       <c r="D26">
-        <v>1185.748779014189</v>
+        <v>1096.686516434552</v>
       </c>
       <c r="E26">
-        <v>247.724</v>
+        <v>260.175</v>
       </c>
       <c r="F26">
-        <v>298.824</v>
+        <v>311.275</v>
       </c>
       <c r="G26">
         <v>76</v>
@@ -3419,45 +3419,45 @@
         <v>46.969</v>
       </c>
       <c r="M26">
-        <v>22.6508592</v>
+        <v>28.01475</v>
       </c>
       <c r="N26">
-        <v>24.3181408</v>
+        <v>18.95425000000001</v>
       </c>
       <c r="O26">
-        <v>7.29544224</v>
+        <v>5.686275000000001</v>
       </c>
       <c r="P26">
-        <v>17.02269856</v>
+        <v>13.267975</v>
       </c>
       <c r="Q26">
-        <v>17.95369856</v>
+        <v>14.198975</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.083447583185666</v>
+        <v>0.08382622267172875</v>
       </c>
       <c r="T26">
-        <v>0.5182331532885944</v>
+        <v>0.5234452683360372</v>
       </c>
       <c r="U26">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V26">
         <v>0.3</v>
       </c>
       <c r="W26">
-        <v>0.05306</v>
+        <v>0.063</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y26">
-        <v>2.073607874442132</v>
+        <v>1.676581086748945</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07861966700379656</v>
+        <v>0.07869917078648694</v>
       </c>
       <c r="C27">
-        <v>861.4115164345516</v>
+        <v>846.3102755805209</v>
       </c>
       <c r="D27">
-        <v>1096.686516434552</v>
+        <v>1094.036275580521</v>
       </c>
       <c r="E27">
-        <v>260.175</v>
+        <v>272.626</v>
       </c>
       <c r="F27">
-        <v>311.275</v>
+        <v>323.726</v>
       </c>
       <c r="G27">
         <v>76</v>
@@ -3501,28 +3501,28 @@
         <v>46.969</v>
       </c>
       <c r="M27">
-        <v>28.01475</v>
+        <v>29.13534</v>
       </c>
       <c r="N27">
-        <v>18.95425000000001</v>
+        <v>17.83366</v>
       </c>
       <c r="O27">
-        <v>5.686275000000001</v>
+        <v>5.350098</v>
       </c>
       <c r="P27">
-        <v>13.267975</v>
+        <v>12.483562</v>
       </c>
       <c r="Q27">
-        <v>14.198975</v>
+        <v>13.414562</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08382622267172875</v>
+        <v>0.08421509565741479</v>
       </c>
       <c r="T27">
-        <v>0.5234452683360372</v>
+        <v>0.5287982513577352</v>
       </c>
       <c r="U27">
         <v>0.09</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>1.676581086748945</v>
+        <v>1.612097198797062</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07869917078648694</v>
+        <v>0.07877867456917734</v>
       </c>
       <c r="C28">
-        <v>846.3102755805209</v>
+        <v>831.2218129339641</v>
       </c>
       <c r="D28">
-        <v>1094.036275580521</v>
+        <v>1091.398812933964</v>
       </c>
       <c r="E28">
-        <v>272.626</v>
+        <v>285.077</v>
       </c>
       <c r="F28">
-        <v>323.726</v>
+        <v>336.177</v>
       </c>
       <c r="G28">
         <v>76</v>
@@ -3583,28 +3583,28 @@
         <v>46.969</v>
       </c>
       <c r="M28">
-        <v>29.13534</v>
+        <v>30.25593</v>
       </c>
       <c r="N28">
-        <v>17.83366</v>
+        <v>16.71307</v>
       </c>
       <c r="O28">
-        <v>5.350098</v>
+        <v>5.013921000000001</v>
       </c>
       <c r="P28">
-        <v>12.483562</v>
+        <v>11.699149</v>
       </c>
       <c r="Q28">
-        <v>13.414562</v>
+        <v>12.630149</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08421509565741479</v>
+        <v>0.08461462269750321</v>
       </c>
       <c r="T28">
-        <v>0.5287982513577352</v>
+        <v>0.5342978914485208</v>
       </c>
       <c r="U28">
         <v>0.09</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>1.612097198797062</v>
+        <v>1.552389895137912</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07877867456917734</v>
+        <v>0.09121828246332134</v>
       </c>
       <c r="C29">
-        <v>831.2218129339641</v>
+        <v>519.8477239775107</v>
       </c>
       <c r="D29">
-        <v>1091.398812933964</v>
+        <v>792.4757239775107</v>
       </c>
       <c r="E29">
-        <v>285.077</v>
+        <v>297.528</v>
       </c>
       <c r="F29">
-        <v>336.177</v>
+        <v>348.628</v>
       </c>
       <c r="G29">
         <v>76</v>
@@ -3665,45 +3665,45 @@
         <v>46.969</v>
       </c>
       <c r="M29">
-        <v>30.25593</v>
+        <v>51.1785904</v>
       </c>
       <c r="N29">
-        <v>16.71307</v>
+        <v>-4.209590400000003</v>
       </c>
       <c r="O29">
-        <v>5.013921000000001</v>
+        <v>-1.262877120000001</v>
       </c>
       <c r="P29">
-        <v>11.699149</v>
+        <v>-2.946713280000003</v>
       </c>
       <c r="Q29">
-        <v>12.630149</v>
+        <v>-2.015713280000003</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08461462269750321</v>
+        <v>0.08532111777621765</v>
       </c>
       <c r="T29">
-        <v>0.5342978914485208</v>
+        <v>0.5440230621352931</v>
       </c>
       <c r="U29">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V29">
-        <v>0.3</v>
+        <v>0.2753241128735738</v>
       </c>
       <c r="W29">
-        <v>0.063</v>
+        <v>0.1063824202301594</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y29">
-        <v>1.552389895137912</v>
+        <v>0.9177470429119126</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09121828246332134</v>
+        <v>0.09222828246332133</v>
       </c>
       <c r="C30">
-        <v>519.8477239775107</v>
+        <v>490.1572217010781</v>
       </c>
       <c r="D30">
-        <v>792.4757239775107</v>
+        <v>775.2362217010781</v>
       </c>
       <c r="E30">
-        <v>297.528</v>
+        <v>309.979</v>
       </c>
       <c r="F30">
-        <v>348.628</v>
+        <v>361.079</v>
       </c>
       <c r="G30">
         <v>76</v>
@@ -3747,37 +3747,37 @@
         <v>46.969</v>
       </c>
       <c r="M30">
-        <v>51.1785904</v>
+        <v>53.00639720000001</v>
       </c>
       <c r="N30">
-        <v>-4.209590400000003</v>
+        <v>-6.037397200000008</v>
       </c>
       <c r="O30">
-        <v>-1.262877120000001</v>
+        <v>-1.811219160000002</v>
       </c>
       <c r="P30">
-        <v>-2.946713280000003</v>
+        <v>-4.226178040000006</v>
       </c>
       <c r="Q30">
-        <v>-2.015713280000003</v>
+        <v>-3.295178040000006</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08532111777621765</v>
+        <v>0.08587775323785451</v>
       </c>
       <c r="T30">
-        <v>0.5440230621352931</v>
+        <v>0.551685358785086</v>
       </c>
       <c r="U30">
         <v>0.1468</v>
       </c>
       <c r="V30">
-        <v>0.2753241128735738</v>
+        <v>0.2658301779468988</v>
       </c>
       <c r="W30">
-        <v>0.1063824202301594</v>
+        <v>0.1077761298773953</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.9177470429119126</v>
+        <v>0.8861005931563293</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09222828246332132</v>
+        <v>0.09323828246332133</v>
       </c>
       <c r="C31">
-        <v>490.1572217010784</v>
+        <v>461.2008057530305</v>
       </c>
       <c r="D31">
-        <v>775.2362217010783</v>
+        <v>758.7308057530305</v>
       </c>
       <c r="E31">
-        <v>309.9789999999999</v>
+        <v>322.4299999999999</v>
       </c>
       <c r="F31">
-        <v>361.079</v>
+        <v>373.53</v>
       </c>
       <c r="G31">
         <v>76</v>
@@ -3829,37 +3829,37 @@
         <v>46.969</v>
       </c>
       <c r="M31">
-        <v>53.00639719999999</v>
+        <v>54.834204</v>
       </c>
       <c r="N31">
-        <v>-6.037397199999994</v>
+        <v>-7.865203999999999</v>
       </c>
       <c r="O31">
-        <v>-1.811219159999998</v>
+        <v>-2.359561199999999</v>
       </c>
       <c r="P31">
-        <v>-4.226178039999995</v>
+        <v>-5.505642799999999</v>
       </c>
       <c r="Q31">
-        <v>-3.295178039999995</v>
+        <v>-4.574642799999999</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08587775323785451</v>
+        <v>0.08645029256982387</v>
       </c>
       <c r="T31">
-        <v>0.551685358785086</v>
+        <v>0.5595665781963014</v>
       </c>
       <c r="U31">
         <v>0.1468</v>
       </c>
       <c r="V31">
-        <v>0.2658301779468988</v>
+        <v>0.2569691720153355</v>
       </c>
       <c r="W31">
-        <v>0.1077761298773953</v>
+        <v>0.1090769255481488</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.8861005931563295</v>
+        <v>0.8565639067177852</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09323828246332133</v>
+        <v>0.09424828246332133</v>
       </c>
       <c r="C32">
-        <v>461.2008057530305</v>
+        <v>432.9325657014206</v>
       </c>
       <c r="D32">
-        <v>758.7308057530305</v>
+        <v>742.9135657014206</v>
       </c>
       <c r="E32">
-        <v>322.4299999999999</v>
+        <v>334.881</v>
       </c>
       <c r="F32">
-        <v>373.53</v>
+        <v>385.981</v>
       </c>
       <c r="G32">
         <v>76</v>
@@ -3911,37 +3911,37 @@
         <v>46.969</v>
       </c>
       <c r="M32">
-        <v>54.834204</v>
+        <v>56.6620108</v>
       </c>
       <c r="N32">
-        <v>-7.865203999999999</v>
+        <v>-9.693010800000003</v>
       </c>
       <c r="O32">
-        <v>-2.359561199999999</v>
+        <v>-2.907903240000001</v>
       </c>
       <c r="P32">
-        <v>-5.505642799999999</v>
+        <v>-6.785107560000002</v>
       </c>
       <c r="Q32">
-        <v>-4.574642799999999</v>
+        <v>-5.854107560000002</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.08645029256982387</v>
+        <v>0.08703942724474885</v>
       </c>
       <c r="T32">
-        <v>0.5595665781963014</v>
+        <v>0.5676762387498711</v>
       </c>
       <c r="U32">
         <v>0.1468</v>
       </c>
       <c r="V32">
-        <v>0.2569691720153355</v>
+        <v>0.2486798438858086</v>
       </c>
       <c r="W32">
-        <v>0.1090769255481488</v>
+        <v>0.1102937989175633</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.8565639067177852</v>
+        <v>0.8289328129526953</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09424828246332133</v>
+        <v>0.09525828246332133</v>
       </c>
       <c r="C33">
-        <v>432.9325657014206</v>
+        <v>405.3103413081172</v>
       </c>
       <c r="D33">
-        <v>742.9135657014206</v>
+        <v>727.7423413081171</v>
       </c>
       <c r="E33">
-        <v>334.881</v>
+        <v>347.3319999999999</v>
       </c>
       <c r="F33">
-        <v>385.981</v>
+        <v>398.432</v>
       </c>
       <c r="G33">
         <v>76</v>
@@ -3993,37 +3993,37 @@
         <v>46.969</v>
       </c>
       <c r="M33">
-        <v>56.6620108</v>
+        <v>58.4898176</v>
       </c>
       <c r="N33">
-        <v>-9.693010800000003</v>
+        <v>-11.5208176</v>
       </c>
       <c r="O33">
-        <v>-2.907903240000001</v>
+        <v>-3.45624528</v>
       </c>
       <c r="P33">
-        <v>-6.785107560000002</v>
+        <v>-8.06457232</v>
       </c>
       <c r="Q33">
-        <v>-5.854107560000002</v>
+        <v>-7.13357232</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.08703942724474885</v>
+        <v>0.08764588941011281</v>
       </c>
       <c r="T33">
-        <v>0.5676762387498711</v>
+        <v>0.5760244187314868</v>
       </c>
       <c r="U33">
         <v>0.1468</v>
       </c>
       <c r="V33">
-        <v>0.2486798438858086</v>
+        <v>0.2409085987643771</v>
       </c>
       <c r="W33">
-        <v>0.1102937989175633</v>
+        <v>0.1114346177013895</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.8289328129526953</v>
+        <v>0.8030286625479235</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09525828246332133</v>
+        <v>0.1147274799356004</v>
       </c>
       <c r="C34">
-        <v>405.3103413081172</v>
+        <v>187.3018573393969</v>
       </c>
       <c r="D34">
-        <v>727.7423413081171</v>
+        <v>522.1848573393969</v>
       </c>
       <c r="E34">
-        <v>347.3319999999999</v>
+        <v>359.783</v>
       </c>
       <c r="F34">
-        <v>398.432</v>
+        <v>410.883</v>
       </c>
       <c r="G34">
         <v>76</v>
@@ -4075,45 +4075,45 @@
         <v>46.969</v>
       </c>
       <c r="M34">
-        <v>58.4898176</v>
+        <v>82.50530639999999</v>
       </c>
       <c r="N34">
-        <v>-11.5208176</v>
+        <v>-35.53630639999999</v>
       </c>
       <c r="O34">
-        <v>-3.45624528</v>
+        <v>-10.66089192</v>
       </c>
       <c r="P34">
-        <v>-8.06457232</v>
+        <v>-24.87541448</v>
       </c>
       <c r="Q34">
-        <v>-7.13357232</v>
+        <v>-23.94441448</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.08764588941011281</v>
+        <v>0.0892244810017251</v>
       </c>
       <c r="T34">
-        <v>0.5760244187314868</v>
+        <v>0.597754326179771</v>
       </c>
       <c r="U34">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V34">
-        <v>0.2409085987643771</v>
+        <v>0.1707853787208043</v>
       </c>
       <c r="W34">
-        <v>0.1114346177013895</v>
+        <v>0.1665062959528625</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y34">
-        <v>0.8030286625479235</v>
+        <v>0.5692845957360144</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1147274799356004</v>
+        <v>0.1162774799356004</v>
       </c>
       <c r="C35">
-        <v>187.3018573393969</v>
+        <v>163.3665288756711</v>
       </c>
       <c r="D35">
-        <v>522.1848573393969</v>
+        <v>510.7005288756711</v>
       </c>
       <c r="E35">
-        <v>359.783</v>
+        <v>372.234</v>
       </c>
       <c r="F35">
-        <v>410.883</v>
+        <v>423.334</v>
       </c>
       <c r="G35">
         <v>76</v>
@@ -4157,37 +4157,37 @@
         <v>46.969</v>
       </c>
       <c r="M35">
-        <v>82.50530639999999</v>
+        <v>85.0054672</v>
       </c>
       <c r="N35">
-        <v>-35.53630639999999</v>
+        <v>-38.0364672</v>
       </c>
       <c r="O35">
-        <v>-10.66089192</v>
+        <v>-11.41094016</v>
       </c>
       <c r="P35">
-        <v>-24.87541448</v>
+        <v>-26.62552704</v>
       </c>
       <c r="Q35">
-        <v>-23.94441448</v>
+        <v>-25.69452704</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.0892244810017251</v>
+        <v>0.08988242768356942</v>
       </c>
       <c r="T35">
-        <v>0.597754326179771</v>
+        <v>0.6068112099097676</v>
       </c>
       <c r="U35">
         <v>0.2008</v>
       </c>
       <c r="V35">
-        <v>0.1707853787208043</v>
+        <v>0.165762279346663</v>
       </c>
       <c r="W35">
-        <v>0.1665062959528625</v>
+        <v>0.1675149343071901</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.5692845957360144</v>
+        <v>0.5525409311555434</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1162774799356004</v>
+        <v>0.1178274799356004</v>
       </c>
       <c r="C36">
-        <v>163.3665288756711</v>
+        <v>139.9254759060955</v>
       </c>
       <c r="D36">
-        <v>510.7005288756711</v>
+        <v>499.7104759060956</v>
       </c>
       <c r="E36">
-        <v>372.234</v>
+        <v>384.685</v>
       </c>
       <c r="F36">
-        <v>423.334</v>
+        <v>435.785</v>
       </c>
       <c r="G36">
         <v>76</v>
@@ -4239,37 +4239,37 @@
         <v>46.969</v>
       </c>
       <c r="M36">
-        <v>85.0054672</v>
+        <v>87.505628</v>
       </c>
       <c r="N36">
-        <v>-38.0364672</v>
+        <v>-40.536628</v>
       </c>
       <c r="O36">
-        <v>-11.41094016</v>
+        <v>-12.1609884</v>
       </c>
       <c r="P36">
-        <v>-26.62552704</v>
+        <v>-28.3756396</v>
       </c>
       <c r="Q36">
-        <v>-25.69452704</v>
+        <v>-27.4446396</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.08988242768356942</v>
+        <v>0.09056061887870126</v>
       </c>
       <c r="T36">
-        <v>0.6068112099097676</v>
+        <v>0.6161467669853025</v>
       </c>
       <c r="U36">
         <v>0.2008</v>
       </c>
       <c r="V36">
-        <v>0.165762279346663</v>
+        <v>0.1610262142224727</v>
       </c>
       <c r="W36">
-        <v>0.1675149343071901</v>
+        <v>0.1684659361841275</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.5525409311555434</v>
+        <v>0.5367540474082422</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1178274799356004</v>
+        <v>0.1193774799356004</v>
       </c>
       <c r="C37">
-        <v>139.9254759060955</v>
+        <v>116.9474608692611</v>
       </c>
       <c r="D37">
-        <v>499.7104759060956</v>
+        <v>489.1834608692612</v>
       </c>
       <c r="E37">
-        <v>384.685</v>
+        <v>397.136</v>
       </c>
       <c r="F37">
-        <v>435.785</v>
+        <v>448.236</v>
       </c>
       <c r="G37">
         <v>76</v>
@@ -4321,37 +4321,37 @@
         <v>46.969</v>
       </c>
       <c r="M37">
-        <v>87.505628</v>
+        <v>90.00578880000002</v>
       </c>
       <c r="N37">
-        <v>-40.536628</v>
+        <v>-43.03678880000002</v>
       </c>
       <c r="O37">
-        <v>-12.1609884</v>
+        <v>-12.91103664</v>
       </c>
       <c r="P37">
-        <v>-28.3756396</v>
+        <v>-30.12575216000001</v>
       </c>
       <c r="Q37">
-        <v>-27.4446396</v>
+        <v>-29.19475216000001</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09056061887870126</v>
+        <v>0.09126000354868097</v>
       </c>
       <c r="T37">
-        <v>0.6161467669853025</v>
+        <v>0.6257740602194478</v>
       </c>
       <c r="U37">
         <v>0.2008</v>
       </c>
       <c r="V37">
-        <v>0.1610262142224727</v>
+        <v>0.1565532638274039</v>
       </c>
       <c r="W37">
-        <v>0.1684659361841275</v>
+        <v>0.1693641046234573</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.5367540474082422</v>
+        <v>0.5218442127580131</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1193774799356004</v>
+        <v>0.1209274799356005</v>
       </c>
       <c r="C38">
-        <v>116.9474608692612</v>
+        <v>94.40382412705554</v>
       </c>
       <c r="D38">
-        <v>489.1834608692612</v>
+        <v>479.0908241270555</v>
       </c>
       <c r="E38">
-        <v>397.1359999999999</v>
+        <v>409.5869999999999</v>
       </c>
       <c r="F38">
-        <v>448.2359999999999</v>
+        <v>460.687</v>
       </c>
       <c r="G38">
         <v>76</v>
@@ -4403,37 +4403,37 @@
         <v>46.969</v>
       </c>
       <c r="M38">
-        <v>90.00578879999999</v>
+        <v>92.50594959999999</v>
       </c>
       <c r="N38">
-        <v>-43.03678879999999</v>
+        <v>-45.53694959999999</v>
       </c>
       <c r="O38">
-        <v>-12.91103664</v>
+        <v>-13.66108488</v>
       </c>
       <c r="P38">
-        <v>-30.12575215999999</v>
+        <v>-31.87586472</v>
       </c>
       <c r="Q38">
-        <v>-29.19475215999999</v>
+        <v>-30.94486471999999</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09126000354868097</v>
+        <v>0.09198159090659655</v>
       </c>
       <c r="T38">
-        <v>0.6257740602194477</v>
+        <v>0.6357069818102327</v>
       </c>
       <c r="U38">
         <v>0.2008</v>
       </c>
       <c r="V38">
-        <v>0.156553263827404</v>
+        <v>0.1523220945347714</v>
       </c>
       <c r="W38">
-        <v>0.1693641046234573</v>
+        <v>0.1702137234174179</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.5218442127580132</v>
+        <v>0.5077403151159048</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1209274799356005</v>
+        <v>0.1360354038363143</v>
       </c>
       <c r="C39">
-        <v>94.40382412705554</v>
+        <v>1.739654963745807</v>
       </c>
       <c r="D39">
-        <v>479.0908241270555</v>
+        <v>398.8776549637458</v>
       </c>
       <c r="E39">
-        <v>409.5869999999999</v>
+        <v>422.038</v>
       </c>
       <c r="F39">
-        <v>460.687</v>
+        <v>473.138</v>
       </c>
       <c r="G39">
         <v>76</v>
@@ -4485,45 +4485,45 @@
         <v>46.969</v>
       </c>
       <c r="M39">
-        <v>92.50594959999999</v>
+        <v>111.5659404</v>
       </c>
       <c r="N39">
-        <v>-45.53694959999999</v>
+        <v>-64.59694039999999</v>
       </c>
       <c r="O39">
-        <v>-13.66108488</v>
+        <v>-19.37908212</v>
       </c>
       <c r="P39">
-        <v>-31.87586472</v>
+        <v>-45.21785828</v>
       </c>
       <c r="Q39">
-        <v>-30.94486471999999</v>
+        <v>-44.28685828</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.09198159090659655</v>
+        <v>0.09314246156753178</v>
       </c>
       <c r="T39">
-        <v>0.6357069818102327</v>
+        <v>0.6516868034155076</v>
       </c>
       <c r="U39">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.1523220945347714</v>
+        <v>0.1262992984192154</v>
       </c>
       <c r="W39">
-        <v>0.1702137234174179</v>
+        <v>0.206018625432749</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y39">
-        <v>0.5077403151159048</v>
+        <v>0.4209976613973847</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1360354038363143</v>
+        <v>0.1379354038363143</v>
       </c>
       <c r="C40">
-        <v>1.739654963745807</v>
+        <v>-18.93692947909807</v>
       </c>
       <c r="D40">
-        <v>398.8776549637458</v>
+        <v>390.6520705209019</v>
       </c>
       <c r="E40">
-        <v>422.038</v>
+        <v>434.489</v>
       </c>
       <c r="F40">
-        <v>473.138</v>
+        <v>485.589</v>
       </c>
       <c r="G40">
         <v>76</v>
@@ -4567,37 +4567,37 @@
         <v>46.969</v>
       </c>
       <c r="M40">
-        <v>111.5659404</v>
+        <v>114.5018862</v>
       </c>
       <c r="N40">
-        <v>-64.59694039999999</v>
+        <v>-67.53288620000001</v>
       </c>
       <c r="O40">
-        <v>-19.37908212</v>
+        <v>-20.25986586</v>
       </c>
       <c r="P40">
-        <v>-45.21785828</v>
+        <v>-47.27302034</v>
       </c>
       <c r="Q40">
-        <v>-44.28685828</v>
+        <v>-46.34202034</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09314246156753178</v>
+        <v>0.09391856749486838</v>
       </c>
       <c r="T40">
-        <v>0.6516868034155076</v>
+        <v>0.6623701936354339</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.1262992984192154</v>
+        <v>0.1230608548700047</v>
       </c>
       <c r="W40">
-        <v>0.206018625432749</v>
+        <v>0.2067822504216529</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.4209976613973847</v>
+        <v>0.4102028495666824</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1379354038363143</v>
+        <v>0.1398354038363143</v>
       </c>
       <c r="C41">
-        <v>-18.93692947909807</v>
+        <v>-39.2811154889302</v>
       </c>
       <c r="D41">
-        <v>390.6520705209019</v>
+        <v>382.7588845110698</v>
       </c>
       <c r="E41">
-        <v>434.489</v>
+        <v>446.9399999999999</v>
       </c>
       <c r="F41">
-        <v>485.589</v>
+        <v>498.04</v>
       </c>
       <c r="G41">
         <v>76</v>
@@ -4649,37 +4649,37 @@
         <v>46.969</v>
       </c>
       <c r="M41">
-        <v>114.5018862</v>
+        <v>117.437832</v>
       </c>
       <c r="N41">
-        <v>-67.53288620000001</v>
+        <v>-70.46883199999999</v>
       </c>
       <c r="O41">
-        <v>-20.25986586</v>
+        <v>-21.1406496</v>
       </c>
       <c r="P41">
-        <v>-47.27302034</v>
+        <v>-49.3281824</v>
       </c>
       <c r="Q41">
-        <v>-46.34202034</v>
+        <v>-48.3971824</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.09391856749486838</v>
+        <v>0.09472054361978285</v>
       </c>
       <c r="T41">
-        <v>0.6623701936354339</v>
+        <v>0.6734096968626911</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.1230608548700047</v>
+        <v>0.1199843334982546</v>
       </c>
       <c r="W41">
-        <v>0.2067822504216529</v>
+        <v>0.2075076941611116</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.4102028495666824</v>
+        <v>0.3999477783275155</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1398354038363143</v>
+        <v>0.1417354038363143</v>
       </c>
       <c r="C42">
-        <v>-39.2811154889302</v>
+        <v>-59.31265251165291</v>
       </c>
       <c r="D42">
-        <v>382.7588845110698</v>
+        <v>375.1783474883471</v>
       </c>
       <c r="E42">
-        <v>446.9399999999999</v>
+        <v>459.391</v>
       </c>
       <c r="F42">
-        <v>498.04</v>
+        <v>510.491</v>
       </c>
       <c r="G42">
         <v>76</v>
@@ -4731,37 +4731,37 @@
         <v>46.969</v>
       </c>
       <c r="M42">
-        <v>117.437832</v>
+        <v>120.3737778</v>
       </c>
       <c r="N42">
-        <v>-70.46883199999999</v>
+        <v>-73.40477780000001</v>
       </c>
       <c r="O42">
-        <v>-21.1406496</v>
+        <v>-22.02143334</v>
       </c>
       <c r="P42">
-        <v>-49.3281824</v>
+        <v>-51.38334446</v>
       </c>
       <c r="Q42">
-        <v>-48.3971824</v>
+        <v>-50.45234446000001</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.09472054361978285</v>
+        <v>0.09554970537605036</v>
       </c>
       <c r="T42">
-        <v>0.6734096968626911</v>
+        <v>0.68482342053833</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.1199843334982546</v>
+        <v>0.1170578863397606</v>
       </c>
       <c r="W42">
-        <v>0.2075076941611116</v>
+        <v>0.2081977504010844</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.3999477783275155</v>
+        <v>0.3901929544658687</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1417354038363143</v>
+        <v>0.1436354038363143</v>
       </c>
       <c r="C43">
-        <v>-59.31265251165291</v>
+        <v>-79.04975582677281</v>
       </c>
       <c r="D43">
-        <v>375.1783474883471</v>
+        <v>367.8922441732272</v>
       </c>
       <c r="E43">
-        <v>459.391</v>
+        <v>471.842</v>
       </c>
       <c r="F43">
-        <v>510.491</v>
+        <v>522.942</v>
       </c>
       <c r="G43">
         <v>76</v>
@@ -4813,37 +4813,37 @@
         <v>46.969</v>
       </c>
       <c r="M43">
-        <v>120.3737778</v>
+        <v>123.3097236</v>
       </c>
       <c r="N43">
-        <v>-73.40477780000001</v>
+        <v>-76.34072360000002</v>
       </c>
       <c r="O43">
-        <v>-22.02143334</v>
+        <v>-22.90221708</v>
       </c>
       <c r="P43">
-        <v>-51.38334446</v>
+        <v>-53.43850652000002</v>
       </c>
       <c r="Q43">
-        <v>-50.45234446000001</v>
+        <v>-52.50750652000002</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.09554970537605036</v>
+        <v>0.09640745891701674</v>
       </c>
       <c r="T43">
-        <v>0.68482342053833</v>
+        <v>0.6966307208924392</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.1170578863397606</v>
+        <v>0.1142707938078615</v>
       </c>
       <c r="W43">
-        <v>0.2081977504010844</v>
+        <v>0.2088549468201062</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.3901929544658687</v>
+        <v>0.380902646026205</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1436354038363143</v>
+        <v>0.1455354038363144</v>
       </c>
       <c r="C44">
-        <v>-79.0497558267727</v>
+        <v>-98.50925267986946</v>
       </c>
       <c r="D44">
-        <v>367.8922441732272</v>
+        <v>360.8837473201305</v>
       </c>
       <c r="E44">
-        <v>471.8419999999999</v>
+        <v>484.2929999999999</v>
       </c>
       <c r="F44">
-        <v>522.9419999999999</v>
+        <v>535.3929999999999</v>
       </c>
       <c r="G44">
         <v>76</v>
@@ -4895,37 +4895,37 @@
         <v>46.969</v>
       </c>
       <c r="M44">
-        <v>123.3097236</v>
+        <v>126.2456694</v>
       </c>
       <c r="N44">
-        <v>-76.34072359999999</v>
+        <v>-79.27666939999997</v>
       </c>
       <c r="O44">
-        <v>-22.90221708</v>
+        <v>-23.78300081999999</v>
       </c>
       <c r="P44">
-        <v>-53.43850651999999</v>
+        <v>-55.49366857999998</v>
       </c>
       <c r="Q44">
-        <v>-52.50750651999999</v>
+        <v>-54.56266857999999</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.09640745891701674</v>
+        <v>0.09729530907345563</v>
       </c>
       <c r="T44">
-        <v>0.6966307208924392</v>
+        <v>0.7088523124870432</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.1142707938078616</v>
+        <v>0.1116133334867485</v>
       </c>
       <c r="W44">
-        <v>0.2088549468201062</v>
+        <v>0.2094815759638247</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.3809026460262052</v>
+        <v>0.3720444449558284</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1455354038363144</v>
+        <v>0.1474354038363143</v>
       </c>
       <c r="C45">
-        <v>-98.50925267986946</v>
+        <v>-117.7067120240222</v>
       </c>
       <c r="D45">
-        <v>360.8837473201305</v>
+        <v>354.1372879759778</v>
       </c>
       <c r="E45">
-        <v>484.2929999999999</v>
+        <v>496.7439999999999</v>
       </c>
       <c r="F45">
-        <v>535.3929999999999</v>
+        <v>547.8439999999999</v>
       </c>
       <c r="G45">
         <v>76</v>
@@ -4977,37 +4977,37 @@
         <v>46.969</v>
       </c>
       <c r="M45">
-        <v>126.2456694</v>
+        <v>129.1816152</v>
       </c>
       <c r="N45">
-        <v>-79.27666939999997</v>
+        <v>-82.21261519999999</v>
       </c>
       <c r="O45">
-        <v>-23.78300081999999</v>
+        <v>-24.66378456</v>
       </c>
       <c r="P45">
-        <v>-55.49366857999998</v>
+        <v>-57.54883063999999</v>
       </c>
       <c r="Q45">
-        <v>-54.56266857999999</v>
+        <v>-56.61783063999999</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.09729530907345563</v>
+        <v>0.09821486816405305</v>
       </c>
       <c r="T45">
-        <v>0.7088523124870432</v>
+        <v>0.7215103894957404</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.1116133334867485</v>
+        <v>0.1090766668165951</v>
       </c>
       <c r="W45">
-        <v>0.2094815759638247</v>
+        <v>0.2100797219646469</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.3720444449558284</v>
+        <v>0.3635888893886504</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1474354038363143</v>
+        <v>0.1493354038363143</v>
       </c>
       <c r="C46">
-        <v>-117.7067120240222</v>
+        <v>-136.6565599757636</v>
       </c>
       <c r="D46">
-        <v>354.1372879759778</v>
+        <v>347.6384400242363</v>
       </c>
       <c r="E46">
-        <v>496.7439999999999</v>
+        <v>509.1949999999999</v>
       </c>
       <c r="F46">
-        <v>547.8439999999999</v>
+        <v>560.295</v>
       </c>
       <c r="G46">
         <v>76</v>
@@ -5059,37 +5059,37 @@
         <v>46.969</v>
       </c>
       <c r="M46">
-        <v>129.1816152</v>
+        <v>132.117561</v>
       </c>
       <c r="N46">
-        <v>-82.21261519999999</v>
+        <v>-85.148561</v>
       </c>
       <c r="O46">
-        <v>-24.66378456</v>
+        <v>-25.5445683</v>
       </c>
       <c r="P46">
-        <v>-57.54883063999999</v>
+        <v>-59.60399270000001</v>
       </c>
       <c r="Q46">
-        <v>-56.61783063999999</v>
+        <v>-58.67299270000001</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.09821486816405305</v>
+        <v>0.09916786576703583</v>
       </c>
       <c r="T46">
-        <v>0.7215103894957404</v>
+        <v>0.7346287602138448</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.1090766668165951</v>
+        <v>0.1066527408873374</v>
       </c>
       <c r="W46">
-        <v>0.2100797219646469</v>
+        <v>0.2106512836987658</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.3635888893886504</v>
+        <v>0.3555091362911248</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1493354038363143</v>
+        <v>0.1512354038363143</v>
       </c>
       <c r="C47">
-        <v>-136.6565599757636</v>
+        <v>-155.3721827875801</v>
       </c>
       <c r="D47">
-        <v>347.6384400242363</v>
+        <v>341.3738172124199</v>
       </c>
       <c r="E47">
-        <v>509.1949999999999</v>
+        <v>521.646</v>
       </c>
       <c r="F47">
-        <v>560.295</v>
+        <v>572.746</v>
       </c>
       <c r="G47">
         <v>76</v>
@@ -5141,37 +5141,37 @@
         <v>46.969</v>
       </c>
       <c r="M47">
-        <v>132.117561</v>
+        <v>135.0535068</v>
       </c>
       <c r="N47">
-        <v>-85.148561</v>
+        <v>-88.08450680000001</v>
       </c>
       <c r="O47">
-        <v>-25.5445683</v>
+        <v>-26.42535204</v>
       </c>
       <c r="P47">
-        <v>-59.60399270000001</v>
+        <v>-61.65915476000001</v>
       </c>
       <c r="Q47">
-        <v>-58.67299270000001</v>
+        <v>-60.72815476000001</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.09916786576703583</v>
+        <v>0.1001561595775365</v>
       </c>
       <c r="T47">
-        <v>0.7346287602138448</v>
+        <v>0.7482329965141012</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.1066527408873374</v>
+        <v>0.1043342030419605</v>
       </c>
       <c r="W47">
-        <v>0.2106512836987658</v>
+        <v>0.2111979949227057</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.3555091362911248</v>
+        <v>0.3477806768065351</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1512354038363143</v>
+        <v>0.1531354038363144</v>
       </c>
       <c r="C48">
-        <v>-155.3721827875801</v>
+        <v>-173.8660188837924</v>
       </c>
       <c r="D48">
-        <v>341.3738172124199</v>
+        <v>335.3309811162076</v>
       </c>
       <c r="E48">
-        <v>521.646</v>
+        <v>534.097</v>
       </c>
       <c r="F48">
-        <v>572.746</v>
+        <v>585.197</v>
       </c>
       <c r="G48">
         <v>76</v>
@@ -5223,37 +5223,37 @@
         <v>46.969</v>
       </c>
       <c r="M48">
-        <v>135.0535068</v>
+        <v>137.9894526</v>
       </c>
       <c r="N48">
-        <v>-88.08450680000001</v>
+        <v>-91.0204526</v>
       </c>
       <c r="O48">
-        <v>-26.42535204</v>
+        <v>-27.30613578</v>
       </c>
       <c r="P48">
-        <v>-61.65915476000001</v>
+        <v>-63.71431682</v>
       </c>
       <c r="Q48">
-        <v>-60.72815476000001</v>
+        <v>-62.78331682</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1001561595775365</v>
+        <v>0.1011817474940938</v>
       </c>
       <c r="T48">
-        <v>0.7482329965141012</v>
+        <v>0.7623506002219146</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.1043342030419605</v>
+        <v>0.1021143263814933</v>
       </c>
       <c r="W48">
-        <v>0.2111979949227057</v>
+        <v>0.2117214418392439</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.3477806768065351</v>
+        <v>0.340381087938311</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1531354038363144</v>
+        <v>0.1550354038363143</v>
       </c>
       <c r="C49">
-        <v>-173.8660188837924</v>
+        <v>-192.1496412914096</v>
       </c>
       <c r="D49">
-        <v>335.3309811162076</v>
+        <v>329.4983587085904</v>
       </c>
       <c r="E49">
-        <v>534.097</v>
+        <v>546.548</v>
       </c>
       <c r="F49">
-        <v>585.197</v>
+        <v>597.648</v>
       </c>
       <c r="G49">
         <v>76</v>
@@ -5305,37 +5305,37 @@
         <v>46.969</v>
       </c>
       <c r="M49">
-        <v>137.9894526</v>
+        <v>140.9253984</v>
       </c>
       <c r="N49">
-        <v>-91.0204526</v>
+        <v>-93.95639840000001</v>
       </c>
       <c r="O49">
-        <v>-27.30613578</v>
+        <v>-28.18691952</v>
       </c>
       <c r="P49">
-        <v>-63.71431682</v>
+        <v>-65.76947888000001</v>
       </c>
       <c r="Q49">
-        <v>-62.78331682</v>
+        <v>-64.83847888000001</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1011817474940938</v>
+        <v>0.1022467810997494</v>
       </c>
       <c r="T49">
-        <v>0.7623506002219146</v>
+        <v>0.7770111886877206</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.1021143263814933</v>
+        <v>0.09998694458187886</v>
       </c>
       <c r="W49">
-        <v>0.2117214418392439</v>
+        <v>0.212223078467593</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.340381087938311</v>
+        <v>0.3332898152729294</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1550354038363143</v>
+        <v>0.1569354038363143</v>
       </c>
       <c r="C50">
-        <v>-192.1496412914095</v>
+        <v>-210.2338316154252</v>
       </c>
       <c r="D50">
-        <v>329.4983587085904</v>
+        <v>323.8651683845747</v>
       </c>
       <c r="E50">
-        <v>546.5479999999999</v>
+        <v>558.9989999999999</v>
       </c>
       <c r="F50">
-        <v>597.6479999999999</v>
+        <v>610.0989999999999</v>
       </c>
       <c r="G50">
         <v>76</v>
@@ -5387,37 +5387,37 @@
         <v>46.969</v>
       </c>
       <c r="M50">
-        <v>140.9253984</v>
+        <v>143.8613442</v>
       </c>
       <c r="N50">
-        <v>-93.95639839999998</v>
+        <v>-96.8923442</v>
       </c>
       <c r="O50">
-        <v>-28.18691951999999</v>
+        <v>-29.06770326</v>
       </c>
       <c r="P50">
-        <v>-65.76947887999999</v>
+        <v>-67.82464093999999</v>
       </c>
       <c r="Q50">
-        <v>-64.83847888</v>
+        <v>-66.89364094</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1022467810997494</v>
+        <v>0.1033535807291563</v>
       </c>
       <c r="T50">
-        <v>0.7770111886877205</v>
+        <v>0.7922467021914013</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.09998694458187889</v>
+        <v>0.09794639469245277</v>
       </c>
       <c r="W50">
-        <v>0.212223078467593</v>
+        <v>0.2127042401315196</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.3332898152729296</v>
+        <v>0.3264879823081759</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1569354038363143</v>
+        <v>0.1588354038363143</v>
       </c>
       <c r="C51">
-        <v>-210.2338316154252</v>
+        <v>-228.1286465534581</v>
       </c>
       <c r="D51">
-        <v>323.8651683845747</v>
+        <v>318.4213534465419</v>
       </c>
       <c r="E51">
-        <v>558.9989999999999</v>
+        <v>571.4499999999999</v>
       </c>
       <c r="F51">
-        <v>610.0989999999999</v>
+        <v>622.55</v>
       </c>
       <c r="G51">
         <v>76</v>
@@ -5469,37 +5469,37 @@
         <v>46.969</v>
       </c>
       <c r="M51">
-        <v>143.8613442</v>
+        <v>146.79729</v>
       </c>
       <c r="N51">
-        <v>-96.8923442</v>
+        <v>-99.82829000000001</v>
       </c>
       <c r="O51">
-        <v>-29.06770326</v>
+        <v>-29.948487</v>
       </c>
       <c r="P51">
-        <v>-67.82464093999999</v>
+        <v>-69.87980300000001</v>
       </c>
       <c r="Q51">
-        <v>-66.89364094</v>
+        <v>-68.94880300000001</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1033535807291563</v>
+        <v>0.1045046523437394</v>
       </c>
       <c r="T51">
-        <v>0.7922467021914013</v>
+        <v>0.8080916362352293</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.09794639469245277</v>
+        <v>0.0959874667986037</v>
       </c>
       <c r="W51">
-        <v>0.2127042401315196</v>
+        <v>0.2131661553288892</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.3264879823081759</v>
+        <v>0.3199582226620123</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1588354038363143</v>
+        <v>0.1607354038363143</v>
       </c>
       <c r="C52">
-        <v>-228.1286465534581</v>
+        <v>-245.8434778130588</v>
       </c>
       <c r="D52">
-        <v>318.4213534465419</v>
+        <v>313.1575221869412</v>
       </c>
       <c r="E52">
-        <v>571.4499999999999</v>
+        <v>583.901</v>
       </c>
       <c r="F52">
-        <v>622.55</v>
+        <v>635.001</v>
       </c>
       <c r="G52">
         <v>76</v>
@@ -5551,37 +5551,37 @@
         <v>46.969</v>
       </c>
       <c r="M52">
-        <v>146.79729</v>
+        <v>149.7332358</v>
       </c>
       <c r="N52">
-        <v>-99.82829000000001</v>
+        <v>-102.7642358</v>
       </c>
       <c r="O52">
-        <v>-29.948487</v>
+        <v>-30.82927074</v>
       </c>
       <c r="P52">
-        <v>-69.87980300000001</v>
+        <v>-71.93496506</v>
       </c>
       <c r="Q52">
-        <v>-68.94880300000001</v>
+        <v>-71.00396506</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1045046523437394</v>
+        <v>0.1057027064732035</v>
       </c>
       <c r="T52">
-        <v>0.8080916362352293</v>
+        <v>0.8245833022808463</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.0959874667986037</v>
+        <v>0.09410535960647422</v>
       </c>
       <c r="W52">
-        <v>0.2131661553288892</v>
+        <v>0.2136099562047934</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.3199582226620123</v>
+        <v>0.3136845320215808</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1607354038363143</v>
+        <v>0.1626354038363143</v>
       </c>
       <c r="C53">
-        <v>-245.8434778130588</v>
+        <v>-263.387106182699</v>
       </c>
       <c r="D53">
-        <v>313.1575221869412</v>
+        <v>308.064893817301</v>
       </c>
       <c r="E53">
-        <v>583.901</v>
+        <v>596.352</v>
       </c>
       <c r="F53">
-        <v>635.001</v>
+        <v>647.452</v>
       </c>
       <c r="G53">
         <v>76</v>
@@ -5633,37 +5633,37 @@
         <v>46.969</v>
       </c>
       <c r="M53">
-        <v>149.7332358</v>
+        <v>152.6691816</v>
       </c>
       <c r="N53">
-        <v>-102.7642358</v>
+        <v>-105.7001816</v>
       </c>
       <c r="O53">
-        <v>-30.82927074</v>
+        <v>-31.71005448</v>
       </c>
       <c r="P53">
-        <v>-71.93496506</v>
+        <v>-73.99012712000001</v>
       </c>
       <c r="Q53">
-        <v>-71.00396506</v>
+        <v>-73.05912712000001</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1057027064732035</v>
+        <v>0.1069506795247286</v>
       </c>
       <c r="T53">
-        <v>0.8245833022808463</v>
+        <v>0.841762121078364</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.09410535960647422</v>
+        <v>0.09229564115250356</v>
       </c>
       <c r="W53">
-        <v>0.2136099562047934</v>
+        <v>0.2140366878162397</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.3136845320215808</v>
+        <v>0.3076521371750118</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1626354038363143</v>
+        <v>0.1645354038363143</v>
       </c>
       <c r="C54">
-        <v>-263.387106182699</v>
+        <v>-280.767750411305</v>
       </c>
       <c r="D54">
-        <v>308.064893817301</v>
+        <v>303.135249588695</v>
       </c>
       <c r="E54">
-        <v>596.352</v>
+        <v>608.803</v>
       </c>
       <c r="F54">
-        <v>647.452</v>
+        <v>659.903</v>
       </c>
       <c r="G54">
         <v>76</v>
@@ -5715,37 +5715,37 @@
         <v>46.969</v>
       </c>
       <c r="M54">
-        <v>152.6691816</v>
+        <v>155.6051274</v>
       </c>
       <c r="N54">
-        <v>-105.7001816</v>
+        <v>-108.6361274</v>
       </c>
       <c r="O54">
-        <v>-31.71005448</v>
+        <v>-32.59083822</v>
       </c>
       <c r="P54">
-        <v>-73.99012712000001</v>
+        <v>-76.04528918000003</v>
       </c>
       <c r="Q54">
-        <v>-73.05912712000001</v>
+        <v>-75.11428918000003</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1069506795247286</v>
+        <v>0.1082517578124887</v>
       </c>
       <c r="T54">
-        <v>0.841762121078364</v>
+        <v>0.8596719534417335</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.09229564115250356</v>
+        <v>0.09055421396094689</v>
       </c>
       <c r="W54">
-        <v>0.2140366878162397</v>
+        <v>0.2144473163480087</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.3076521371750118</v>
+        <v>0.3018473798698229</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1645354038363143</v>
+        <v>0.1664354038363143</v>
       </c>
       <c r="C55">
-        <v>-280.767750411305</v>
+        <v>-297.9931114686942</v>
       </c>
       <c r="D55">
-        <v>303.135249588695</v>
+        <v>298.3608885313059</v>
       </c>
       <c r="E55">
-        <v>608.803</v>
+        <v>621.254</v>
       </c>
       <c r="F55">
-        <v>659.903</v>
+        <v>672.354</v>
       </c>
       <c r="G55">
         <v>76</v>
@@ -5797,37 +5797,37 @@
         <v>46.969</v>
       </c>
       <c r="M55">
-        <v>155.6051274</v>
+        <v>158.5410732</v>
       </c>
       <c r="N55">
-        <v>-108.6361274</v>
+        <v>-111.5720732</v>
       </c>
       <c r="O55">
-        <v>-32.59083822</v>
+        <v>-33.47162196000001</v>
       </c>
       <c r="P55">
-        <v>-76.04528918000003</v>
+        <v>-78.10045124000003</v>
       </c>
       <c r="Q55">
-        <v>-75.11428918000003</v>
+        <v>-77.16945124000003</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1082517578124887</v>
+        <v>0.1096094047214559</v>
       </c>
       <c r="T55">
-        <v>0.8596719534417335</v>
+        <v>0.8783604741687276</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.09055421396094689</v>
+        <v>0.0888772840727812</v>
       </c>
       <c r="W55">
-        <v>0.2144473163480087</v>
+        <v>0.2148427364156382</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.3018473798698229</v>
+        <v>0.2962576135759373</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1664354038363143</v>
+        <v>0.1683354038363143</v>
       </c>
       <c r="C56">
-        <v>-297.9931114686942</v>
+        <v>-315.0704126882726</v>
       </c>
       <c r="D56">
-        <v>298.3608885313059</v>
+        <v>293.7345873117274</v>
       </c>
       <c r="E56">
-        <v>621.254</v>
+        <v>633.7049999999999</v>
       </c>
       <c r="F56">
-        <v>672.354</v>
+        <v>684.8049999999999</v>
       </c>
       <c r="G56">
         <v>76</v>
@@ -5879,37 +5879,37 @@
         <v>46.969</v>
       </c>
       <c r="M56">
-        <v>158.5410732</v>
+        <v>161.477019</v>
       </c>
       <c r="N56">
-        <v>-111.5720732</v>
+        <v>-114.508019</v>
       </c>
       <c r="O56">
-        <v>-33.47162196000001</v>
+        <v>-34.3524057</v>
       </c>
       <c r="P56">
-        <v>-78.10045124000003</v>
+        <v>-80.1556133</v>
       </c>
       <c r="Q56">
-        <v>-77.16945124000003</v>
+        <v>-79.2246133</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1096094047214559</v>
+        <v>0.1110273914930438</v>
       </c>
       <c r="T56">
-        <v>0.8783604741687276</v>
+        <v>0.8978795958169217</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.0888772840727812</v>
+        <v>0.08726133345327611</v>
       </c>
       <c r="W56">
-        <v>0.2148427364156382</v>
+        <v>0.2152237775717175</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.2962576135759373</v>
+        <v>0.2908711115109203</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1683354038363143</v>
+        <v>0.1702354038363144</v>
       </c>
       <c r="C57">
-        <v>-315.0704126882726</v>
+        <v>-332.006436232106</v>
       </c>
       <c r="D57">
-        <v>293.7345873117274</v>
+        <v>289.249563767894</v>
       </c>
       <c r="E57">
-        <v>633.7049999999999</v>
+        <v>646.1559999999999</v>
       </c>
       <c r="F57">
-        <v>684.8049999999999</v>
+        <v>697.256</v>
       </c>
       <c r="G57">
         <v>76</v>
@@ -5961,37 +5961,37 @@
         <v>46.969</v>
       </c>
       <c r="M57">
-        <v>161.477019</v>
+        <v>164.4129648</v>
       </c>
       <c r="N57">
-        <v>-114.508019</v>
+        <v>-117.4439648</v>
       </c>
       <c r="O57">
-        <v>-34.3524057</v>
+        <v>-35.23318944</v>
       </c>
       <c r="P57">
-        <v>-80.1556133</v>
+        <v>-82.21077536000001</v>
       </c>
       <c r="Q57">
-        <v>-79.2246133</v>
+        <v>-81.27977536000002</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1110273914930438</v>
+        <v>0.1125098322087948</v>
       </c>
       <c r="T57">
-        <v>0.8978795958169217</v>
+        <v>0.9182859502673061</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.08726133345327611</v>
+        <v>0.08570309535589617</v>
       </c>
       <c r="W57">
-        <v>0.2152237775717175</v>
+        <v>0.2155912101150797</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.2908711115109203</v>
+        <v>0.2856769845196538</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1702354038363144</v>
+        <v>0.1721354038363143</v>
       </c>
       <c r="C58">
-        <v>-332.006436232106</v>
+        <v>-348.8075562655295</v>
       </c>
       <c r="D58">
-        <v>289.249563767894</v>
+        <v>284.8994437344705</v>
       </c>
       <c r="E58">
-        <v>646.1559999999999</v>
+        <v>658.607</v>
       </c>
       <c r="F58">
-        <v>697.256</v>
+        <v>709.707</v>
       </c>
       <c r="G58">
         <v>76</v>
@@ -6043,37 +6043,37 @@
         <v>46.969</v>
       </c>
       <c r="M58">
-        <v>164.4129648</v>
+        <v>167.3489106</v>
       </c>
       <c r="N58">
-        <v>-117.4439648</v>
+        <v>-120.3799106</v>
       </c>
       <c r="O58">
-        <v>-35.23318944</v>
+        <v>-36.11397318</v>
       </c>
       <c r="P58">
-        <v>-82.21077536000001</v>
+        <v>-84.26593742000001</v>
       </c>
       <c r="Q58">
-        <v>-81.27977536000002</v>
+        <v>-83.33493742000002</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1125098322087948</v>
+        <v>0.114061223655511</v>
       </c>
       <c r="T58">
-        <v>0.9182859502673061</v>
+        <v>0.939641437482825</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.08570309535589617</v>
+        <v>0.08419953227947694</v>
       </c>
       <c r="W58">
-        <v>0.2155912101150797</v>
+        <v>0.2159457502884993</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.2856769845196538</v>
+        <v>0.2806651075982564</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1721354038363143</v>
+        <v>0.1740354038363144</v>
       </c>
       <c r="C59">
-        <v>-348.8075562655295</v>
+        <v>-365.4797691825681</v>
       </c>
       <c r="D59">
-        <v>284.8994437344705</v>
+        <v>280.6782308174319</v>
       </c>
       <c r="E59">
-        <v>658.607</v>
+        <v>671.058</v>
       </c>
       <c r="F59">
-        <v>709.707</v>
+        <v>722.158</v>
       </c>
       <c r="G59">
         <v>76</v>
@@ -6125,37 +6125,37 @@
         <v>46.969</v>
       </c>
       <c r="M59">
-        <v>167.3489106</v>
+        <v>170.2848564</v>
       </c>
       <c r="N59">
-        <v>-120.3799106</v>
+        <v>-123.3158564</v>
       </c>
       <c r="O59">
-        <v>-36.11397318</v>
+        <v>-36.99475692000001</v>
       </c>
       <c r="P59">
-        <v>-84.26593742000001</v>
+        <v>-86.32109948000002</v>
       </c>
       <c r="Q59">
-        <v>-83.33493742000002</v>
+        <v>-85.39009948000002</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.114061223655511</v>
+        <v>0.1156864908854041</v>
       </c>
       <c r="T59">
-        <v>0.939641437482825</v>
+        <v>0.9620138526609875</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.08419953227947694</v>
+        <v>0.08274781620569284</v>
       </c>
       <c r="W59">
-        <v>0.2159457502884993</v>
+        <v>0.2162880649386976</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.2806651075982564</v>
+        <v>0.2758260540189761</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1740354038363143</v>
+        <v>0.1759354038363143</v>
       </c>
       <c r="C60">
-        <v>-365.4797691825678</v>
+        <v>-382.0287211835767</v>
       </c>
       <c r="D60">
-        <v>280.6782308174321</v>
+        <v>276.5802788164232</v>
       </c>
       <c r="E60">
-        <v>671.0579999999999</v>
+        <v>683.5089999999999</v>
       </c>
       <c r="F60">
-        <v>722.1579999999999</v>
+        <v>734.6089999999999</v>
       </c>
       <c r="G60">
         <v>76</v>
@@ -6207,37 +6207,37 @@
         <v>46.969</v>
       </c>
       <c r="M60">
-        <v>170.2848564</v>
+        <v>173.2208022</v>
       </c>
       <c r="N60">
-        <v>-123.3158564</v>
+        <v>-126.2518022</v>
       </c>
       <c r="O60">
-        <v>-36.99475692</v>
+        <v>-37.87554065999999</v>
       </c>
       <c r="P60">
-        <v>-86.32109948</v>
+        <v>-88.37626154</v>
       </c>
       <c r="Q60">
-        <v>-85.39009948</v>
+        <v>-87.44526154</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1156864908854041</v>
+        <v>0.1173910394435846</v>
       </c>
       <c r="T60">
-        <v>0.9620138526609872</v>
+        <v>0.9854776051649138</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.08274781620569285</v>
+        <v>0.08134531084627433</v>
       </c>
       <c r="W60">
-        <v>0.2162880649386976</v>
+        <v>0.2166187757024485</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.2758260540189762</v>
+        <v>0.2711510361542477</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1759354038363143</v>
+        <v>0.1778354038363144</v>
       </c>
       <c r="C61">
-        <v>-382.0287211835767</v>
+        <v>-398.4597334718163</v>
       </c>
       <c r="D61">
-        <v>276.5802788164232</v>
+        <v>272.6002665281836</v>
       </c>
       <c r="E61">
-        <v>683.5089999999999</v>
+        <v>695.9599999999999</v>
       </c>
       <c r="F61">
-        <v>734.6089999999999</v>
+        <v>747.0599999999999</v>
       </c>
       <c r="G61">
         <v>76</v>
@@ -6289,37 +6289,37 @@
         <v>46.969</v>
       </c>
       <c r="M61">
-        <v>173.2208022</v>
+        <v>176.156748</v>
       </c>
       <c r="N61">
-        <v>-126.2518022</v>
+        <v>-129.187748</v>
       </c>
       <c r="O61">
-        <v>-37.87554065999999</v>
+        <v>-38.7563244</v>
       </c>
       <c r="P61">
-        <v>-88.37626154</v>
+        <v>-90.4314236</v>
       </c>
       <c r="Q61">
-        <v>-87.44526154</v>
+        <v>-89.5004236</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1173910394435846</v>
+        <v>0.1191808154296743</v>
       </c>
       <c r="T61">
-        <v>0.9854776051649138</v>
+        <v>1.010114545294037</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.08134531084627433</v>
+        <v>0.07998955566550309</v>
       </c>
       <c r="W61">
-        <v>0.2166187757024485</v>
+        <v>0.2169384627740744</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.2711510361542477</v>
+        <v>0.2666318522183436</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1778354038363144</v>
+        <v>0.1797354038363143</v>
       </c>
       <c r="C62">
-        <v>-398.4597334718163</v>
+        <v>-414.777825305403</v>
       </c>
       <c r="D62">
-        <v>272.6002665281836</v>
+        <v>268.7331746945969</v>
       </c>
       <c r="E62">
-        <v>695.9599999999999</v>
+        <v>708.4109999999999</v>
       </c>
       <c r="F62">
-        <v>747.0599999999999</v>
+        <v>759.511</v>
       </c>
       <c r="G62">
         <v>76</v>
@@ -6371,37 +6371,37 @@
         <v>46.969</v>
       </c>
       <c r="M62">
-        <v>176.156748</v>
+        <v>179.0926938</v>
       </c>
       <c r="N62">
-        <v>-129.187748</v>
+        <v>-132.1236938</v>
       </c>
       <c r="O62">
-        <v>-38.7563244</v>
+        <v>-39.63710814</v>
       </c>
       <c r="P62">
-        <v>-90.4314236</v>
+        <v>-92.48658566</v>
       </c>
       <c r="Q62">
-        <v>-89.5004236</v>
+        <v>-91.55558566000001</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1191808154296743</v>
+        <v>0.1210623747996659</v>
       </c>
       <c r="T62">
-        <v>1.010114545294037</v>
+        <v>1.036014918250294</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.07998955566550309</v>
+        <v>0.07867825147426533</v>
       </c>
       <c r="W62">
-        <v>0.2169384627740744</v>
+        <v>0.2172476683023682</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.2666318522183436</v>
+        <v>0.2622608382475511</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1797354038363143</v>
+        <v>0.1816354038363143</v>
       </c>
       <c r="C63">
-        <v>-414.777825305403</v>
+        <v>-430.9877351146234</v>
       </c>
       <c r="D63">
-        <v>268.7331746945969</v>
+        <v>264.9742648853766</v>
       </c>
       <c r="E63">
-        <v>708.4109999999999</v>
+        <v>720.862</v>
       </c>
       <c r="F63">
-        <v>759.511</v>
+        <v>771.962</v>
       </c>
       <c r="G63">
         <v>76</v>
@@ -6453,37 +6453,37 @@
         <v>46.969</v>
       </c>
       <c r="M63">
-        <v>179.0926938</v>
+        <v>182.0286396</v>
       </c>
       <c r="N63">
-        <v>-132.1236938</v>
+        <v>-135.0596396</v>
       </c>
       <c r="O63">
-        <v>-39.63710814</v>
+        <v>-40.51789188</v>
       </c>
       <c r="P63">
-        <v>-92.48658566</v>
+        <v>-94.54174771999999</v>
       </c>
       <c r="Q63">
-        <v>-91.55558566000001</v>
+        <v>-93.61074771999999</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1210623747996659</v>
+        <v>0.1230429636101834</v>
       </c>
       <c r="T63">
-        <v>1.036014918250294</v>
+        <v>1.063278468730565</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.07867825147426533</v>
+        <v>0.0774092474182288</v>
       </c>
       <c r="W63">
-        <v>0.2172476683023682</v>
+        <v>0.2175468994587816</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.2622608382475511</v>
+        <v>0.2580308247274293</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1816354038363143</v>
+        <v>0.1835354038363143</v>
       </c>
       <c r="C64">
-        <v>-430.9877351146234</v>
+        <v>-447.0939398714229</v>
       </c>
       <c r="D64">
-        <v>264.9742648853766</v>
+        <v>261.319060128577</v>
       </c>
       <c r="E64">
-        <v>720.862</v>
+        <v>733.3129999999999</v>
       </c>
       <c r="F64">
-        <v>771.962</v>
+        <v>784.4129999999999</v>
       </c>
       <c r="G64">
         <v>76</v>
@@ -6535,37 +6535,37 @@
         <v>46.969</v>
       </c>
       <c r="M64">
-        <v>182.0286396</v>
+        <v>184.9645854</v>
       </c>
       <c r="N64">
-        <v>-135.0596396</v>
+        <v>-137.9955854</v>
       </c>
       <c r="O64">
-        <v>-40.51789188</v>
+        <v>-41.39867561999999</v>
       </c>
       <c r="P64">
-        <v>-94.54174771999999</v>
+        <v>-96.59690977999999</v>
       </c>
       <c r="Q64">
-        <v>-93.61074771999999</v>
+        <v>-95.66590977999999</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1230429636101834</v>
+        <v>0.1251306112753235</v>
       </c>
       <c r="T64">
-        <v>1.063278468730565</v>
+        <v>1.092015724642202</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.0774092474182288</v>
+        <v>0.07618052920524104</v>
       </c>
       <c r="W64">
-        <v>0.2175468994587816</v>
+        <v>0.2178366312134042</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.2580308247274293</v>
+        <v>0.2539350973508034</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1835354038363143</v>
+        <v>0.1854354038363143</v>
       </c>
       <c r="C65">
-        <v>-447.0939398714229</v>
+        <v>-463.1006728775475</v>
       </c>
       <c r="D65">
-        <v>261.319060128577</v>
+        <v>257.7633271224524</v>
       </c>
       <c r="E65">
-        <v>733.3129999999999</v>
+        <v>745.7639999999999</v>
       </c>
       <c r="F65">
-        <v>784.4129999999999</v>
+        <v>796.8639999999999</v>
       </c>
       <c r="G65">
         <v>76</v>
@@ -6617,37 +6617,37 @@
         <v>46.969</v>
       </c>
       <c r="M65">
-        <v>184.9645854</v>
+        <v>187.9005312</v>
       </c>
       <c r="N65">
-        <v>-137.9955854</v>
+        <v>-140.9315312</v>
       </c>
       <c r="O65">
-        <v>-41.39867561999999</v>
+        <v>-42.27945936</v>
       </c>
       <c r="P65">
-        <v>-96.59690977999999</v>
+        <v>-98.65207183999999</v>
       </c>
       <c r="Q65">
-        <v>-95.66590977999999</v>
+        <v>-97.72107183999999</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1251306112753235</v>
+        <v>0.1273342393663048</v>
       </c>
       <c r="T65">
-        <v>1.092015724642202</v>
+        <v>1.122349494771152</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.07618052920524104</v>
+        <v>0.07499020843640915</v>
       </c>
       <c r="W65">
-        <v>0.2178366312134042</v>
+        <v>0.2181173088506947</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.2539350973508034</v>
+        <v>0.2499673614546971</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1854354038363143</v>
+        <v>0.1873354038363143</v>
       </c>
       <c r="C66">
-        <v>-463.1006728775475</v>
+        <v>-479.0119401199335</v>
       </c>
       <c r="D66">
-        <v>257.7633271224524</v>
+        <v>254.3030598800665</v>
       </c>
       <c r="E66">
-        <v>745.7639999999999</v>
+        <v>758.2149999999999</v>
       </c>
       <c r="F66">
-        <v>796.8639999999999</v>
+        <v>809.3149999999999</v>
       </c>
       <c r="G66">
         <v>76</v>
@@ -6699,37 +6699,37 @@
         <v>46.969</v>
       </c>
       <c r="M66">
-        <v>187.9005312</v>
+        <v>190.836477</v>
       </c>
       <c r="N66">
-        <v>-140.9315312</v>
+        <v>-143.867477</v>
       </c>
       <c r="O66">
-        <v>-42.27945936</v>
+        <v>-43.1602431</v>
       </c>
       <c r="P66">
-        <v>-98.65207183999999</v>
+        <v>-100.7072339</v>
       </c>
       <c r="Q66">
-        <v>-97.72107183999999</v>
+        <v>-99.77623390000001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1273342393663048</v>
+        <v>0.1296637890624849</v>
       </c>
       <c r="T66">
-        <v>1.122349494771152</v>
+        <v>1.154416623193185</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.07499020843640915</v>
+        <v>0.07383651292200286</v>
       </c>
       <c r="W66">
-        <v>0.2181173088506947</v>
+        <v>0.2183893502529917</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.2499673614546971</v>
+        <v>0.2461217097400095</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1873354038363143</v>
+        <v>0.1892354038363144</v>
       </c>
       <c r="C67">
-        <v>-479.0119401199335</v>
+        <v>-494.8315353262016</v>
       </c>
       <c r="D67">
-        <v>254.3030598800665</v>
+        <v>250.9344646737984</v>
       </c>
       <c r="E67">
-        <v>758.2149999999999</v>
+        <v>770.6659999999999</v>
       </c>
       <c r="F67">
-        <v>809.3149999999999</v>
+        <v>821.766</v>
       </c>
       <c r="G67">
         <v>76</v>
@@ -6781,37 +6781,37 @@
         <v>46.969</v>
       </c>
       <c r="M67">
-        <v>190.836477</v>
+        <v>193.7724228</v>
       </c>
       <c r="N67">
-        <v>-143.867477</v>
+        <v>-146.8034228</v>
       </c>
       <c r="O67">
-        <v>-43.1602431</v>
+        <v>-44.04102683999999</v>
       </c>
       <c r="P67">
-        <v>-100.7072339</v>
+        <v>-102.76239596</v>
       </c>
       <c r="Q67">
-        <v>-99.77623390000001</v>
+        <v>-101.83139596</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1296637890624849</v>
+        <v>0.1321303710937345</v>
       </c>
       <c r="T67">
-        <v>1.154416623193185</v>
+        <v>1.188370053287102</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.07383651292200286</v>
+        <v>0.07271777787773008</v>
       </c>
       <c r="W67">
-        <v>0.2183893502529917</v>
+        <v>0.2186531479764313</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.2461217097400095</v>
+        <v>0.2423925929257669</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1892354038363144</v>
+        <v>0.1911354038363144</v>
       </c>
       <c r="C68">
-        <v>-494.8315353262016</v>
+        <v>-510.5630538392074</v>
       </c>
       <c r="D68">
-        <v>250.9344646737984</v>
+        <v>247.6539461607926</v>
       </c>
       <c r="E68">
-        <v>770.6659999999999</v>
+        <v>783.117</v>
       </c>
       <c r="F68">
-        <v>821.766</v>
+        <v>834.217</v>
       </c>
       <c r="G68">
         <v>76</v>
@@ -6863,37 +6863,37 @@
         <v>46.969</v>
       </c>
       <c r="M68">
-        <v>193.7724228</v>
+        <v>196.7083686</v>
       </c>
       <c r="N68">
-        <v>-146.8034228</v>
+        <v>-149.7393686</v>
       </c>
       <c r="O68">
-        <v>-44.04102683999999</v>
+        <v>-44.92181058</v>
       </c>
       <c r="P68">
-        <v>-102.76239596</v>
+        <v>-104.81755802</v>
       </c>
       <c r="Q68">
-        <v>-101.83139596</v>
+        <v>-103.88655802</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1321303710937345</v>
+        <v>0.1347464429450597</v>
       </c>
       <c r="T68">
-        <v>1.188370053287102</v>
+        <v>1.224381267023075</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.07271777787773008</v>
+        <v>0.07163243790940575</v>
       </c>
       <c r="W68">
-        <v>0.2186531479764313</v>
+        <v>0.2189090711409621</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.2423925929257669</v>
+        <v>0.2387747930313525</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1911354038363144</v>
+        <v>0.1930354038363143</v>
       </c>
       <c r="C69">
-        <v>-510.5630538392074</v>
+        <v>-526.2099054173279</v>
       </c>
       <c r="D69">
-        <v>247.6539461607926</v>
+        <v>244.4580945826721</v>
       </c>
       <c r="E69">
-        <v>783.117</v>
+        <v>795.568</v>
       </c>
       <c r="F69">
-        <v>834.217</v>
+        <v>846.668</v>
       </c>
       <c r="G69">
         <v>76</v>
@@ -6945,37 +6945,37 @@
         <v>46.969</v>
       </c>
       <c r="M69">
-        <v>196.7083686</v>
+        <v>199.6443144</v>
       </c>
       <c r="N69">
-        <v>-149.7393686</v>
+        <v>-152.6753144</v>
       </c>
       <c r="O69">
-        <v>-44.92181058</v>
+        <v>-45.80259432</v>
       </c>
       <c r="P69">
-        <v>-104.81755802</v>
+        <v>-106.87272008</v>
       </c>
       <c r="Q69">
-        <v>-103.88655802</v>
+        <v>-105.94172008</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1347464429450597</v>
+        <v>0.1375260192870928</v>
       </c>
       <c r="T69">
-        <v>1.224381267023075</v>
+        <v>1.262643181617546</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.07163243790940575</v>
+        <v>0.07057901970485565</v>
       </c>
       <c r="W69">
-        <v>0.2189090711409621</v>
+        <v>0.219157467153595</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2387747930313525</v>
+        <v>0.2352633990161855</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1930354038363143</v>
+        <v>0.1949354038363144</v>
       </c>
       <c r="C70">
-        <v>-526.2099054173279</v>
+        <v>-541.7753260562855</v>
       </c>
       <c r="D70">
-        <v>244.4580945826721</v>
+        <v>241.3436739437145</v>
       </c>
       <c r="E70">
-        <v>795.568</v>
+        <v>808.019</v>
       </c>
       <c r="F70">
-        <v>846.668</v>
+        <v>859.119</v>
       </c>
       <c r="G70">
         <v>76</v>
@@ -7027,37 +7027,37 @@
         <v>46.969</v>
       </c>
       <c r="M70">
-        <v>199.6443144</v>
+        <v>202.5802602</v>
       </c>
       <c r="N70">
-        <v>-152.6753144</v>
+        <v>-155.6112602</v>
       </c>
       <c r="O70">
-        <v>-45.80259432</v>
+        <v>-46.68337806000001</v>
       </c>
       <c r="P70">
-        <v>-106.87272008</v>
+        <v>-108.92788214</v>
       </c>
       <c r="Q70">
-        <v>-105.94172008</v>
+        <v>-107.99688214</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1375260192870928</v>
+        <v>0.1404849231350636</v>
       </c>
       <c r="T70">
-        <v>1.262643181617546</v>
+        <v>1.303373606831015</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.07057901970485565</v>
+        <v>0.06955613536130703</v>
       </c>
       <c r="W70">
-        <v>0.219157467153595</v>
+        <v>0.2193986632818038</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2352633990161855</v>
+        <v>0.23185378453769</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1949354038363144</v>
+        <v>0.1968354038363143</v>
       </c>
       <c r="C71">
-        <v>-541.7753260562855</v>
+        <v>-557.2623889186725</v>
       </c>
       <c r="D71">
-        <v>241.3436739437145</v>
+        <v>238.3076110813276</v>
       </c>
       <c r="E71">
-        <v>808.019</v>
+        <v>820.47</v>
       </c>
       <c r="F71">
-        <v>859.119</v>
+        <v>871.5700000000001</v>
       </c>
       <c r="G71">
         <v>76</v>
@@ -7109,37 +7109,37 @@
         <v>46.969</v>
       </c>
       <c r="M71">
-        <v>202.5802602</v>
+        <v>205.516206</v>
       </c>
       <c r="N71">
-        <v>-155.6112602</v>
+        <v>-158.547206</v>
       </c>
       <c r="O71">
-        <v>-46.68337806000001</v>
+        <v>-47.5641618</v>
       </c>
       <c r="P71">
-        <v>-108.92788214</v>
+        <v>-110.9830442</v>
       </c>
       <c r="Q71">
-        <v>-107.99688214</v>
+        <v>-110.0520442</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1404849231350636</v>
+        <v>0.1436410872395657</v>
       </c>
       <c r="T71">
-        <v>1.303373606831015</v>
+        <v>1.346819393725383</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.06955613536130703</v>
+        <v>0.06856247628471693</v>
       </c>
       <c r="W71">
-        <v>0.2193986632818038</v>
+        <v>0.2196329680920638</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.23185378453769</v>
+        <v>0.2285415876157231</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1968354038363143</v>
+        <v>0.1987354038363144</v>
       </c>
       <c r="C72">
-        <v>-557.2623889186725</v>
+        <v>-572.6740144487763</v>
       </c>
       <c r="D72">
-        <v>238.3076110813276</v>
+        <v>235.3469855512238</v>
       </c>
       <c r="E72">
-        <v>820.47</v>
+        <v>832.921</v>
       </c>
       <c r="F72">
-        <v>871.5700000000001</v>
+        <v>884.0210000000001</v>
       </c>
       <c r="G72">
         <v>76</v>
@@ -7191,37 +7191,37 @@
         <v>46.969</v>
       </c>
       <c r="M72">
-        <v>205.516206</v>
+        <v>208.4521518</v>
       </c>
       <c r="N72">
-        <v>-158.547206</v>
+        <v>-161.4831518</v>
       </c>
       <c r="O72">
-        <v>-47.5641618</v>
+        <v>-48.44494554000001</v>
       </c>
       <c r="P72">
-        <v>-110.9830442</v>
+        <v>-113.03820626</v>
       </c>
       <c r="Q72">
-        <v>-110.0520442</v>
+        <v>-112.10720626</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1436410872395657</v>
+        <v>0.1470149178340335</v>
       </c>
       <c r="T72">
-        <v>1.346819393725383</v>
+        <v>1.393261441784879</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.06856247628471693</v>
+        <v>0.06759680760465049</v>
       </c>
       <c r="W72">
-        <v>0.2196329680920638</v>
+        <v>0.2198606727668234</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2285415876157231</v>
+        <v>0.2253226920155016</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1987354038363143</v>
+        <v>0.2006354038363143</v>
       </c>
       <c r="C73">
-        <v>-572.6740144487761</v>
+        <v>-588.012979742683</v>
       </c>
       <c r="D73">
-        <v>235.3469855512238</v>
+        <v>232.4590202573169</v>
       </c>
       <c r="E73">
-        <v>832.9209999999998</v>
+        <v>845.3719999999998</v>
       </c>
       <c r="F73">
-        <v>884.0209999999998</v>
+        <v>896.4719999999999</v>
       </c>
       <c r="G73">
         <v>76</v>
@@ -7273,37 +7273,37 @@
         <v>46.969</v>
       </c>
       <c r="M73">
-        <v>208.4521518</v>
+        <v>211.3880976</v>
       </c>
       <c r="N73">
-        <v>-161.4831518</v>
+        <v>-164.4190976</v>
       </c>
       <c r="O73">
-        <v>-48.44494553999999</v>
+        <v>-49.32572928</v>
       </c>
       <c r="P73">
-        <v>-113.03820626</v>
+        <v>-115.09336832</v>
       </c>
       <c r="Q73">
-        <v>-112.10720626</v>
+        <v>-114.16236832</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1470149178340335</v>
+        <v>0.1506297363281061</v>
       </c>
       <c r="T73">
-        <v>1.393261441784878</v>
+        <v>1.443020778991481</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.06759680760465051</v>
+        <v>0.06665796305458592</v>
       </c>
       <c r="W73">
-        <v>0.2198606727668234</v>
+        <v>0.2200820523117286</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2253226920155017</v>
+        <v>0.222193210181953</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2006354038363143</v>
+        <v>0.2025354038363144</v>
       </c>
       <c r="C74">
-        <v>-588.012979742683</v>
+        <v>-603.2819272368569</v>
       </c>
       <c r="D74">
-        <v>232.4590202573169</v>
+        <v>229.641072763143</v>
       </c>
       <c r="E74">
-        <v>845.3719999999998</v>
+        <v>857.8229999999999</v>
       </c>
       <c r="F74">
-        <v>896.4719999999999</v>
+        <v>908.9229999999999</v>
       </c>
       <c r="G74">
         <v>76</v>
@@ -7355,37 +7355,37 @@
         <v>46.969</v>
       </c>
       <c r="M74">
-        <v>211.3880976</v>
+        <v>214.3240434</v>
       </c>
       <c r="N74">
-        <v>-164.4190976</v>
+        <v>-167.3550434</v>
       </c>
       <c r="O74">
-        <v>-49.32572928</v>
+        <v>-50.20651302</v>
       </c>
       <c r="P74">
-        <v>-115.09336832</v>
+        <v>-117.14853038</v>
       </c>
       <c r="Q74">
-        <v>-114.16236832</v>
+        <v>-116.21753038</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1506297363281061</v>
+        <v>0.154512319155073</v>
       </c>
       <c r="T74">
-        <v>1.443020778991481</v>
+        <v>1.496465993028202</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.06665796305458592</v>
+        <v>0.06574484027301623</v>
       </c>
       <c r="W74">
-        <v>0.2200820523117286</v>
+        <v>0.2202973666636228</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.222193210181953</v>
+        <v>0.2191494675767208</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2025354038363144</v>
+        <v>0.2044354038363143</v>
       </c>
       <c r="C75">
-        <v>-603.2819272368569</v>
+        <v>-618.4833727723325</v>
       </c>
       <c r="D75">
-        <v>229.641072763143</v>
+        <v>226.8906272276674</v>
       </c>
       <c r="E75">
-        <v>857.8229999999999</v>
+        <v>870.2739999999999</v>
       </c>
       <c r="F75">
-        <v>908.9229999999999</v>
+        <v>921.3739999999999</v>
       </c>
       <c r="G75">
         <v>76</v>
@@ -7437,37 +7437,37 @@
         <v>46.969</v>
       </c>
       <c r="M75">
-        <v>214.3240434</v>
+        <v>217.2599892</v>
       </c>
       <c r="N75">
-        <v>-167.3550434</v>
+        <v>-170.2909892</v>
       </c>
       <c r="O75">
-        <v>-50.20651302</v>
+        <v>-51.08729675999999</v>
       </c>
       <c r="P75">
-        <v>-117.14853038</v>
+        <v>-119.20369244</v>
       </c>
       <c r="Q75">
-        <v>-116.21753038</v>
+        <v>-118.27269244</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.154512319155073</v>
+        <v>0.1586935621994989</v>
       </c>
       <c r="T75">
-        <v>1.496465993028202</v>
+        <v>1.554022377375441</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.06574484027301623</v>
+        <v>0.06485639648554305</v>
       </c>
       <c r="W75">
-        <v>0.2202973666636228</v>
+        <v>0.220506861708709</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2191494675767208</v>
+        <v>0.2161879882851435</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2044354038363143</v>
+        <v>0.2063354038363144</v>
       </c>
       <c r="C76">
-        <v>-618.4833727723325</v>
+        <v>-633.6197130862497</v>
       </c>
       <c r="D76">
-        <v>226.8906272276674</v>
+        <v>224.2052869137503</v>
       </c>
       <c r="E76">
-        <v>870.2739999999999</v>
+        <v>882.7249999999999</v>
       </c>
       <c r="F76">
-        <v>921.3739999999999</v>
+        <v>933.8249999999999</v>
       </c>
       <c r="G76">
         <v>76</v>
@@ -7519,37 +7519,37 @@
         <v>46.969</v>
       </c>
       <c r="M76">
-        <v>217.2599892</v>
+        <v>220.195935</v>
       </c>
       <c r="N76">
-        <v>-170.2909892</v>
+        <v>-173.226935</v>
       </c>
       <c r="O76">
-        <v>-51.08729675999999</v>
+        <v>-51.9680805</v>
       </c>
       <c r="P76">
-        <v>-119.20369244</v>
+        <v>-121.2588545</v>
       </c>
       <c r="Q76">
-        <v>-118.27269244</v>
+        <v>-120.3278545</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1586935621994989</v>
+        <v>0.1632093046874788</v>
       </c>
       <c r="T76">
-        <v>1.554022377375441</v>
+        <v>1.616183272470459</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.06485639648554305</v>
+        <v>0.06399164453240247</v>
       </c>
       <c r="W76">
-        <v>0.220506861708709</v>
+        <v>0.2207107702192595</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2161879882851435</v>
+        <v>0.2133054817746749</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2063354038363144</v>
+        <v>0.2082354038363143</v>
       </c>
       <c r="C77">
-        <v>-633.6197130862497</v>
+        <v>-648.6932327776178</v>
       </c>
       <c r="D77">
-        <v>224.2052869137503</v>
+        <v>221.5827672223821</v>
       </c>
       <c r="E77">
-        <v>882.7249999999999</v>
+        <v>895.1759999999999</v>
       </c>
       <c r="F77">
-        <v>933.8249999999999</v>
+        <v>946.276</v>
       </c>
       <c r="G77">
         <v>76</v>
@@ -7601,37 +7601,37 @@
         <v>46.969</v>
       </c>
       <c r="M77">
-        <v>220.195935</v>
+        <v>223.1318808</v>
       </c>
       <c r="N77">
-        <v>-173.226935</v>
+        <v>-176.1628808</v>
       </c>
       <c r="O77">
-        <v>-51.9680805</v>
+        <v>-52.84886424</v>
       </c>
       <c r="P77">
-        <v>-121.2588545</v>
+        <v>-123.31401656</v>
       </c>
       <c r="Q77">
-        <v>-120.3278545</v>
+        <v>-122.38301656</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1632093046874788</v>
+        <v>0.1681013590494571</v>
       </c>
       <c r="T77">
-        <v>1.616183272470459</v>
+        <v>1.683524242156728</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.06399164453240247</v>
+        <v>0.06314964920960771</v>
       </c>
       <c r="W77">
-        <v>0.2207107702192595</v>
+        <v>0.2209093127163745</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2133054817746749</v>
+        <v>0.2104988306986924</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2082354038363143</v>
+        <v>0.2101354038363143</v>
       </c>
       <c r="C78">
-        <v>-648.6932327776178</v>
+        <v>-663.7061107898683</v>
       </c>
       <c r="D78">
-        <v>221.5827672223821</v>
+        <v>219.0208892101318</v>
       </c>
       <c r="E78">
-        <v>895.1759999999999</v>
+        <v>907.627</v>
       </c>
       <c r="F78">
-        <v>946.276</v>
+        <v>958.727</v>
       </c>
       <c r="G78">
         <v>76</v>
@@ -7683,37 +7683,37 @@
         <v>46.969</v>
       </c>
       <c r="M78">
-        <v>223.1318808</v>
+        <v>226.0678266</v>
       </c>
       <c r="N78">
-        <v>-176.1628808</v>
+        <v>-179.0988266</v>
       </c>
       <c r="O78">
-        <v>-52.84886424</v>
+        <v>-53.72964798</v>
       </c>
       <c r="P78">
-        <v>-123.31401656</v>
+        <v>-125.36917862</v>
       </c>
       <c r="Q78">
-        <v>-122.38301656</v>
+        <v>-124.43817862</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1681013590494571</v>
+        <v>0.1734188094429118</v>
       </c>
       <c r="T78">
-        <v>1.683524242156728</v>
+        <v>1.756720948337455</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.06314964920960771</v>
+        <v>0.06232952389519721</v>
       </c>
       <c r="W78">
-        <v>0.2209093127163745</v>
+        <v>0.2211026982655125</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2104988306986924</v>
+        <v>0.2077650796506574</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2101354038363143</v>
+        <v>0.2120354038363143</v>
       </c>
       <c r="C79">
-        <v>-663.7061107898683</v>
+        <v>-678.6604264488421</v>
       </c>
       <c r="D79">
-        <v>219.0208892101318</v>
+        <v>216.5175735511579</v>
       </c>
       <c r="E79">
-        <v>907.627</v>
+        <v>920.078</v>
       </c>
       <c r="F79">
-        <v>958.727</v>
+        <v>971.178</v>
       </c>
       <c r="G79">
         <v>76</v>
@@ -7765,37 +7765,37 @@
         <v>46.969</v>
       </c>
       <c r="M79">
-        <v>226.0678266</v>
+        <v>229.0037724</v>
       </c>
       <c r="N79">
-        <v>-179.0988266</v>
+        <v>-182.0347724</v>
       </c>
       <c r="O79">
-        <v>-53.72964798</v>
+        <v>-54.61043172</v>
       </c>
       <c r="P79">
-        <v>-125.36917862</v>
+        <v>-127.42434068</v>
       </c>
       <c r="Q79">
-        <v>-124.43817862</v>
+        <v>-126.49334068</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1734188094429118</v>
+        <v>0.1792196644175896</v>
       </c>
       <c r="T79">
-        <v>1.756720948337455</v>
+        <v>1.836571900534612</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.06232952389519721</v>
+        <v>0.06153042743500237</v>
       </c>
       <c r="W79">
-        <v>0.2211026982655125</v>
+        <v>0.2212911252108264</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2077650796506574</v>
+        <v>0.2051014247833413</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2120354038363143</v>
+        <v>0.2139354038363143</v>
       </c>
       <c r="C80">
-        <v>-678.6604264488421</v>
+        <v>-693.558165091393</v>
       </c>
       <c r="D80">
-        <v>216.5175735511579</v>
+        <v>214.070834908607</v>
       </c>
       <c r="E80">
-        <v>920.078</v>
+        <v>932.529</v>
       </c>
       <c r="F80">
-        <v>971.178</v>
+        <v>983.629</v>
       </c>
       <c r="G80">
         <v>76</v>
@@ -7847,37 +7847,37 @@
         <v>46.969</v>
       </c>
       <c r="M80">
-        <v>229.0037724</v>
+        <v>231.9397182</v>
       </c>
       <c r="N80">
-        <v>-182.0347724</v>
+        <v>-184.9707182</v>
       </c>
       <c r="O80">
-        <v>-54.61043172</v>
+        <v>-55.49121546000001</v>
       </c>
       <c r="P80">
-        <v>-127.42434068</v>
+        <v>-129.47950274</v>
       </c>
       <c r="Q80">
-        <v>-126.49334068</v>
+        <v>-128.54850274</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1792196644175896</v>
+        <v>0.1855729817708082</v>
       </c>
       <c r="T80">
-        <v>1.836571900534612</v>
+        <v>1.924027705321975</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.06153042743500237</v>
+        <v>0.06075156126493905</v>
       </c>
       <c r="W80">
-        <v>0.2212911252108264</v>
+        <v>0.2214747818537274</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2051014247833413</v>
+        <v>0.2025052042164635</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2139354038363143</v>
+        <v>0.2158354038363143</v>
       </c>
       <c r="C81">
-        <v>-693.558165091393</v>
+        <v>-708.4012233166192</v>
       </c>
       <c r="D81">
-        <v>214.070834908607</v>
+        <v>211.6787766833808</v>
       </c>
       <c r="E81">
-        <v>932.529</v>
+        <v>944.9799999999999</v>
       </c>
       <c r="F81">
-        <v>983.629</v>
+        <v>996.0799999999999</v>
       </c>
       <c r="G81">
         <v>76</v>
@@ -7929,37 +7929,37 @@
         <v>46.969</v>
       </c>
       <c r="M81">
-        <v>231.9397182</v>
+        <v>234.875664</v>
       </c>
       <c r="N81">
-        <v>-184.9707182</v>
+        <v>-187.906664</v>
       </c>
       <c r="O81">
-        <v>-55.49121546000001</v>
+        <v>-56.3719992</v>
       </c>
       <c r="P81">
-        <v>-129.47950274</v>
+        <v>-131.5346648</v>
       </c>
       <c r="Q81">
-        <v>-128.54850274</v>
+        <v>-130.6036648</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1855729817708082</v>
+        <v>0.1925616308593486</v>
       </c>
       <c r="T81">
-        <v>1.924027705321975</v>
+        <v>2.020229090588074</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.06075156126493905</v>
+        <v>0.05999216674912732</v>
       </c>
       <c r="W81">
-        <v>0.2214747818537274</v>
+        <v>0.2216538470805558</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2025052042164635</v>
+        <v>0.1999738891637577</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2158354038363143</v>
+        <v>0.2177354038363143</v>
       </c>
       <c r="C82">
-        <v>-708.4012233166192</v>
+        <v>-723.1914138889186</v>
       </c>
       <c r="D82">
-        <v>211.6787766833808</v>
+        <v>209.3395861110813</v>
       </c>
       <c r="E82">
-        <v>944.9799999999999</v>
+        <v>957.4309999999999</v>
       </c>
       <c r="F82">
-        <v>996.0799999999999</v>
+        <v>1008.531</v>
       </c>
       <c r="G82">
         <v>76</v>
@@ -8011,37 +8011,37 @@
         <v>46.969</v>
       </c>
       <c r="M82">
-        <v>234.875664</v>
+        <v>237.8116098</v>
       </c>
       <c r="N82">
-        <v>-187.906664</v>
+        <v>-190.8426098</v>
       </c>
       <c r="O82">
-        <v>-56.3719992</v>
+        <v>-57.25278294</v>
       </c>
       <c r="P82">
-        <v>-131.5346648</v>
+        <v>-133.58982686</v>
       </c>
       <c r="Q82">
-        <v>-130.6036648</v>
+        <v>-132.65882686</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1925616308593486</v>
+        <v>0.2002859272203669</v>
       </c>
       <c r="T82">
-        <v>2.020229090588074</v>
+        <v>2.12655693746113</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.05999216674912732</v>
+        <v>0.05925152271518747</v>
       </c>
       <c r="W82">
-        <v>0.2216538470805558</v>
+        <v>0.2218284909437588</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.1999738891637577</v>
+        <v>0.1975050757172916</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2177354038363143</v>
+        <v>0.2196354038363143</v>
       </c>
       <c r="C83">
-        <v>-723.1914138889186</v>
+        <v>-737.9304703195041</v>
       </c>
       <c r="D83">
-        <v>209.3395861110813</v>
+        <v>207.0515296804959</v>
       </c>
       <c r="E83">
-        <v>957.4309999999999</v>
+        <v>969.8819999999999</v>
       </c>
       <c r="F83">
-        <v>1008.531</v>
+        <v>1020.982</v>
       </c>
       <c r="G83">
         <v>76</v>
@@ -8093,37 +8093,37 @@
         <v>46.969</v>
       </c>
       <c r="M83">
-        <v>237.8116098</v>
+        <v>240.7475556</v>
       </c>
       <c r="N83">
-        <v>-190.8426098</v>
+        <v>-193.7785556</v>
       </c>
       <c r="O83">
-        <v>-57.25278294</v>
+        <v>-58.13356668</v>
       </c>
       <c r="P83">
-        <v>-133.58982686</v>
+        <v>-135.64498892</v>
       </c>
       <c r="Q83">
-        <v>-132.65882686</v>
+        <v>-134.71398892</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2002859272203669</v>
+        <v>0.2088684787326095</v>
       </c>
       <c r="T83">
-        <v>2.12655693746113</v>
+        <v>2.244698989542304</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.05925152271518747</v>
+        <v>0.05852894316988031</v>
       </c>
       <c r="W83">
-        <v>0.2218284909437588</v>
+        <v>0.2219988752005422</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.1975050757172916</v>
+        <v>0.1950964772329343</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2196354038363143</v>
+        <v>0.2215354038363144</v>
       </c>
       <c r="C84">
-        <v>-737.9304703195041</v>
+        <v>-752.6200511507141</v>
       </c>
       <c r="D84">
-        <v>207.0515296804959</v>
+        <v>204.8129488492859</v>
       </c>
       <c r="E84">
-        <v>969.8819999999999</v>
+        <v>982.333</v>
       </c>
       <c r="F84">
-        <v>1020.982</v>
+        <v>1033.433</v>
       </c>
       <c r="G84">
         <v>76</v>
@@ -8175,37 +8175,37 @@
         <v>46.969</v>
       </c>
       <c r="M84">
-        <v>240.7475556</v>
+        <v>243.6835014</v>
       </c>
       <c r="N84">
-        <v>-193.7785556</v>
+        <v>-196.7145014</v>
       </c>
       <c r="O84">
-        <v>-58.13356668</v>
+        <v>-59.01435042</v>
       </c>
       <c r="P84">
-        <v>-135.64498892</v>
+        <v>-137.70015098</v>
       </c>
       <c r="Q84">
-        <v>-134.71398892</v>
+        <v>-136.76915098</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2088684787326095</v>
+        <v>0.2184607421874689</v>
       </c>
       <c r="T84">
-        <v>2.244698989542304</v>
+        <v>2.376740106574205</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.05852894316988031</v>
+        <v>0.05782377517988174</v>
       </c>
       <c r="W84">
-        <v>0.2219988752005422</v>
+        <v>0.2221651538125839</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.1950964772329343</v>
+        <v>0.1927459172662724</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2215354038363144</v>
+        <v>0.2234354038363144</v>
       </c>
       <c r="C85">
-        <v>-752.6200511507141</v>
+        <v>-767.2617439653752</v>
       </c>
       <c r="D85">
-        <v>204.8129488492859</v>
+        <v>202.6222560346248</v>
       </c>
       <c r="E85">
-        <v>982.333</v>
+        <v>994.784</v>
       </c>
       <c r="F85">
-        <v>1033.433</v>
+        <v>1045.884</v>
       </c>
       <c r="G85">
         <v>76</v>
@@ -8257,37 +8257,37 @@
         <v>46.969</v>
       </c>
       <c r="M85">
-        <v>243.6835014</v>
+        <v>246.6194472</v>
       </c>
       <c r="N85">
-        <v>-196.7145014</v>
+        <v>-199.6504472</v>
       </c>
       <c r="O85">
-        <v>-59.01435042</v>
+        <v>-59.89513416</v>
       </c>
       <c r="P85">
-        <v>-137.70015098</v>
+        <v>-139.75531304</v>
       </c>
       <c r="Q85">
-        <v>-136.76915098</v>
+        <v>-138.82431304</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2184607421874689</v>
+        <v>0.2292520385741858</v>
       </c>
       <c r="T85">
-        <v>2.376740106574205</v>
+        <v>2.525286363235093</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.05782377517988174</v>
+        <v>0.05713539690393077</v>
       </c>
       <c r="W85">
-        <v>0.2221651538125839</v>
+        <v>0.2223274734100531</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.1927459172662724</v>
+        <v>0.1904513230131025</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2234354038363143</v>
+        <v>0.2253354038363143</v>
       </c>
       <c r="C86">
-        <v>-767.261743965375</v>
+        <v>-781.8570691415771</v>
       </c>
       <c r="D86">
-        <v>202.6222560346248</v>
+        <v>200.4779308584228</v>
       </c>
       <c r="E86">
-        <v>994.7839999999998</v>
+        <v>1007.235</v>
       </c>
       <c r="F86">
-        <v>1045.884</v>
+        <v>1058.335</v>
       </c>
       <c r="G86">
         <v>76</v>
@@ -8339,37 +8339,37 @@
         <v>46.969</v>
       </c>
       <c r="M86">
-        <v>246.6194472</v>
+        <v>249.555393</v>
       </c>
       <c r="N86">
-        <v>-199.6504472</v>
+        <v>-202.586393</v>
       </c>
       <c r="O86">
-        <v>-59.89513415999999</v>
+        <v>-60.77591789999998</v>
       </c>
       <c r="P86">
-        <v>-139.75531304</v>
+        <v>-141.8104751</v>
       </c>
       <c r="Q86">
-        <v>-138.82431304</v>
+        <v>-140.8794751</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2292520385741857</v>
+        <v>0.2414821744791314</v>
       </c>
       <c r="T86">
-        <v>2.525286363235091</v>
+        <v>2.693638787450764</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.05713539690393079</v>
+        <v>0.05646321576388454</v>
       </c>
       <c r="W86">
-        <v>0.2223274734100531</v>
+        <v>0.222485973722876</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.1904513230131026</v>
+        <v>0.1882107192129484</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2253354038363143</v>
+        <v>0.2272354038363143</v>
       </c>
       <c r="C87">
-        <v>-781.8570691415771</v>
+        <v>-796.4074833715288</v>
       </c>
       <c r="D87">
-        <v>200.4779308584228</v>
+        <v>198.3785166284711</v>
       </c>
       <c r="E87">
-        <v>1007.235</v>
+        <v>1019.686</v>
       </c>
       <c r="F87">
-        <v>1058.335</v>
+        <v>1070.786</v>
       </c>
       <c r="G87">
         <v>76</v>
@@ -8421,37 +8421,37 @@
         <v>46.969</v>
       </c>
       <c r="M87">
-        <v>249.555393</v>
+        <v>252.4913388</v>
       </c>
       <c r="N87">
-        <v>-202.586393</v>
+        <v>-205.5223388</v>
       </c>
       <c r="O87">
-        <v>-60.77591789999998</v>
+        <v>-61.65670163999999</v>
       </c>
       <c r="P87">
-        <v>-141.8104751</v>
+        <v>-143.86563716</v>
       </c>
       <c r="Q87">
-        <v>-140.8794751</v>
+        <v>-142.93463716</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2414821744791314</v>
+        <v>0.2554594726562122</v>
       </c>
       <c r="T87">
-        <v>2.693638787450764</v>
+        <v>2.886041557982962</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.05646321576388454</v>
+        <v>0.05580666674337426</v>
       </c>
       <c r="W87">
-        <v>0.222485973722876</v>
+        <v>0.2226407879819123</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.1882107192129484</v>
+        <v>0.1860222224779141</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2272354038363143</v>
+        <v>0.2291354038363143</v>
       </c>
       <c r="C88">
-        <v>-796.4074833715288</v>
+        <v>-810.9143829616081</v>
       </c>
       <c r="D88">
-        <v>198.3785166284711</v>
+        <v>196.3226170383917</v>
       </c>
       <c r="E88">
-        <v>1019.686</v>
+        <v>1032.137</v>
       </c>
       <c r="F88">
-        <v>1070.786</v>
+        <v>1083.237</v>
       </c>
       <c r="G88">
         <v>76</v>
@@ -8503,37 +8503,37 @@
         <v>46.969</v>
       </c>
       <c r="M88">
-        <v>252.4913388</v>
+        <v>255.4272846</v>
       </c>
       <c r="N88">
-        <v>-205.5223388</v>
+        <v>-208.4582846</v>
       </c>
       <c r="O88">
-        <v>-61.65670163999999</v>
+        <v>-62.53748537999999</v>
       </c>
       <c r="P88">
-        <v>-143.86563716</v>
+        <v>-145.92079922</v>
       </c>
       <c r="Q88">
-        <v>-142.93463716</v>
+        <v>-144.98979922</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2554594726562122</v>
+        <v>0.2715871243989977</v>
       </c>
       <c r="T88">
-        <v>2.886041557982962</v>
+        <v>3.108044754750882</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.05580666674337426</v>
+        <v>0.05516521080379524</v>
       </c>
       <c r="W88">
-        <v>0.2226407879819123</v>
+        <v>0.2227920432924651</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.1860222224779141</v>
+        <v>0.1838840360126508</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2291354038363143</v>
+        <v>0.2310354038363143</v>
       </c>
       <c r="C89">
-        <v>-810.9143829616081</v>
+        <v>-825.3791069293143</v>
       </c>
       <c r="D89">
-        <v>196.3226170383917</v>
+        <v>194.3088930706855</v>
       </c>
       <c r="E89">
-        <v>1032.137</v>
+        <v>1044.588</v>
       </c>
       <c r="F89">
-        <v>1083.237</v>
+        <v>1095.688</v>
       </c>
       <c r="G89">
         <v>76</v>
@@ -8585,37 +8585,37 @@
         <v>46.969</v>
       </c>
       <c r="M89">
-        <v>255.4272846</v>
+        <v>258.3632304</v>
       </c>
       <c r="N89">
-        <v>-208.4582846</v>
+        <v>-211.3942304</v>
       </c>
       <c r="O89">
-        <v>-62.53748537999999</v>
+        <v>-63.41826911999999</v>
       </c>
       <c r="P89">
-        <v>-145.92079922</v>
+        <v>-147.97596128</v>
       </c>
       <c r="Q89">
-        <v>-144.98979922</v>
+        <v>-147.04496128</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2715871243989977</v>
+        <v>0.2904027180989142</v>
       </c>
       <c r="T89">
-        <v>3.108044754750882</v>
+        <v>3.367048484313456</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.05516521080379524</v>
+        <v>0.05453833340829757</v>
       </c>
       <c r="W89">
-        <v>0.2227920432924651</v>
+        <v>0.2229398609823234</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.1838840360126508</v>
+        <v>0.1817944446943252</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2310354038363143</v>
+        <v>0.2329354038363144</v>
       </c>
       <c r="C90">
-        <v>-825.3791069293143</v>
+        <v>-839.802939911561</v>
       </c>
       <c r="D90">
-        <v>194.3088930706855</v>
+        <v>192.3360600884388</v>
       </c>
       <c r="E90">
-        <v>1044.588</v>
+        <v>1057.039</v>
       </c>
       <c r="F90">
-        <v>1095.688</v>
+        <v>1108.139</v>
       </c>
       <c r="G90">
         <v>76</v>
@@ -8667,37 +8667,37 @@
         <v>46.969</v>
       </c>
       <c r="M90">
-        <v>258.3632304</v>
+        <v>261.2991762</v>
       </c>
       <c r="N90">
-        <v>-211.3942304</v>
+        <v>-214.3301762</v>
       </c>
       <c r="O90">
-        <v>-63.41826911999999</v>
+        <v>-64.29905285999999</v>
       </c>
       <c r="P90">
-        <v>-147.97596128</v>
+        <v>-150.03112334</v>
       </c>
       <c r="Q90">
-        <v>-147.04496128</v>
+        <v>-149.10012334</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2904027180989142</v>
+        <v>0.3126393288351792</v>
       </c>
       <c r="T90">
-        <v>3.367048484313456</v>
+        <v>3.673143801069224</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.05453833340829757</v>
+        <v>0.05392554314528299</v>
       </c>
       <c r="W90">
-        <v>0.2229398609823234</v>
+        <v>0.2230843569263423</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.1817944446943252</v>
+        <v>0.1797518104842766</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2329354038363144</v>
+        <v>0.2348354038363143</v>
       </c>
       <c r="C91">
-        <v>-839.802939911561</v>
+        <v>-854.1871148975781</v>
       </c>
       <c r="D91">
-        <v>192.3360600884388</v>
+        <v>190.4028851024218</v>
       </c>
       <c r="E91">
-        <v>1057.039</v>
+        <v>1069.49</v>
       </c>
       <c r="F91">
-        <v>1108.139</v>
+        <v>1120.59</v>
       </c>
       <c r="G91">
         <v>76</v>
@@ -8749,37 +8749,37 @@
         <v>46.969</v>
       </c>
       <c r="M91">
-        <v>261.2991762</v>
+        <v>264.235122</v>
       </c>
       <c r="N91">
-        <v>-214.3301762</v>
+        <v>-217.266122</v>
       </c>
       <c r="O91">
-        <v>-64.29905285999999</v>
+        <v>-65.1798366</v>
       </c>
       <c r="P91">
-        <v>-150.03112334</v>
+        <v>-152.0862854</v>
       </c>
       <c r="Q91">
-        <v>-149.10012334</v>
+        <v>-151.1552854</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3126393288351792</v>
+        <v>0.3393232617186972</v>
       </c>
       <c r="T91">
-        <v>3.673143801069224</v>
+        <v>4.040458181176148</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.05392554314528299</v>
+        <v>0.05332637044366872</v>
       </c>
       <c r="W91">
-        <v>0.2230843569263423</v>
+        <v>0.2232256418493829</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.1797518104842766</v>
+        <v>0.1777545681455625</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2348354038363143</v>
+        <v>0.2367354038363143</v>
       </c>
       <c r="C92">
-        <v>-854.1871148975781</v>
+        <v>-868.5328157986471</v>
       </c>
       <c r="D92">
-        <v>190.4028851024218</v>
+        <v>188.5081842013528</v>
       </c>
       <c r="E92">
-        <v>1069.49</v>
+        <v>1081.941</v>
       </c>
       <c r="F92">
-        <v>1120.59</v>
+        <v>1133.041</v>
       </c>
       <c r="G92">
         <v>76</v>
@@ -8831,37 +8831,37 @@
         <v>46.969</v>
       </c>
       <c r="M92">
-        <v>264.235122</v>
+        <v>267.1710678</v>
       </c>
       <c r="N92">
-        <v>-217.266122</v>
+        <v>-220.2020678</v>
       </c>
       <c r="O92">
-        <v>-65.1798366</v>
+        <v>-66.06062034</v>
       </c>
       <c r="P92">
-        <v>-152.0862854</v>
+        <v>-154.14144746</v>
       </c>
       <c r="Q92">
-        <v>-151.1552854</v>
+        <v>-153.21044746</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3393232617186972</v>
+        <v>0.3719369574652192</v>
       </c>
       <c r="T92">
-        <v>4.040458181176148</v>
+        <v>4.489397979084609</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.05332637044366872</v>
+        <v>0.05274036637285918</v>
       </c>
       <c r="W92">
-        <v>0.2232256418493829</v>
+        <v>0.2233638216092798</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.1777545681455625</v>
+        <v>0.1758012212428639</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2367354038363143</v>
+        <v>0.2386354038363144</v>
       </c>
       <c r="C93">
-        <v>-868.5328157986471</v>
+        <v>-882.8411798659145</v>
       </c>
       <c r="D93">
-        <v>188.5081842013528</v>
+        <v>186.6508201340855</v>
       </c>
       <c r="E93">
-        <v>1081.941</v>
+        <v>1094.392</v>
       </c>
       <c r="F93">
-        <v>1133.041</v>
+        <v>1145.492</v>
       </c>
       <c r="G93">
         <v>76</v>
@@ -8913,37 +8913,37 @@
         <v>46.969</v>
       </c>
       <c r="M93">
-        <v>267.1710678</v>
+        <v>270.1070136</v>
       </c>
       <c r="N93">
-        <v>-220.2020678</v>
+        <v>-223.1380136</v>
       </c>
       <c r="O93">
-        <v>-66.06062034</v>
+        <v>-66.94140408</v>
       </c>
       <c r="P93">
-        <v>-154.14144746</v>
+        <v>-156.19660952</v>
       </c>
       <c r="Q93">
-        <v>-153.21044746</v>
+        <v>-155.26560952</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3719369574652192</v>
+        <v>0.4127040771483717</v>
       </c>
       <c r="T93">
-        <v>4.489397979084609</v>
+        <v>5.050572726470187</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.05274036637285918</v>
+        <v>0.05216710152098027</v>
       </c>
       <c r="W93">
-        <v>0.2233638216092798</v>
+        <v>0.2234989974613529</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1758012212428639</v>
+        <v>0.1738903384032675</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2386354038363144</v>
+        <v>0.2405354038363144</v>
       </c>
       <c r="C94">
-        <v>-882.8411798659145</v>
+        <v>-897.1132999666686</v>
       </c>
       <c r="D94">
-        <v>186.6508201340855</v>
+        <v>184.8297000333314</v>
       </c>
       <c r="E94">
-        <v>1094.392</v>
+        <v>1106.843</v>
       </c>
       <c r="F94">
-        <v>1145.492</v>
+        <v>1157.943</v>
       </c>
       <c r="G94">
         <v>76</v>
@@ -8995,37 +8995,37 @@
         <v>46.969</v>
       </c>
       <c r="M94">
-        <v>270.1070136</v>
+        <v>273.0429594</v>
       </c>
       <c r="N94">
-        <v>-223.1380136</v>
+        <v>-226.0739594</v>
       </c>
       <c r="O94">
-        <v>-66.94140408</v>
+        <v>-67.82218782000001</v>
       </c>
       <c r="P94">
-        <v>-156.19660952</v>
+        <v>-158.25177158</v>
       </c>
       <c r="Q94">
-        <v>-155.26560952</v>
+        <v>-157.32077158</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4127040771483717</v>
+        <v>0.4651189453124247</v>
       </c>
       <c r="T94">
-        <v>5.050572726470187</v>
+        <v>5.772083115965928</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.05216710152098027</v>
+        <v>0.05160616494548586</v>
       </c>
       <c r="W94">
-        <v>0.2234989974613529</v>
+        <v>0.2236312663058544</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.1738903384032675</v>
+        <v>0.1720205498182862</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2405354038363144</v>
+        <v>0.2424354038363143</v>
       </c>
       <c r="C95">
-        <v>-897.1132999666686</v>
+        <v>-911.350226728645</v>
       </c>
       <c r="D95">
-        <v>184.8297000333314</v>
+        <v>183.043773271355</v>
       </c>
       <c r="E95">
-        <v>1106.843</v>
+        <v>1119.294</v>
       </c>
       <c r="F95">
-        <v>1157.943</v>
+        <v>1170.394</v>
       </c>
       <c r="G95">
         <v>76</v>
@@ -9077,37 +9077,37 @@
         <v>46.969</v>
       </c>
       <c r="M95">
-        <v>273.0429594</v>
+        <v>275.9789052</v>
       </c>
       <c r="N95">
-        <v>-226.0739594</v>
+        <v>-229.0099052</v>
       </c>
       <c r="O95">
-        <v>-67.82218782000001</v>
+        <v>-68.70297155999999</v>
       </c>
       <c r="P95">
-        <v>-158.25177158</v>
+        <v>-160.30693364</v>
       </c>
       <c r="Q95">
-        <v>-157.32077158</v>
+        <v>-159.37593364</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4651189453124247</v>
+        <v>0.535005436197829</v>
       </c>
       <c r="T95">
-        <v>5.772083115965928</v>
+        <v>6.734096968626918</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.05160616494548586</v>
+        <v>0.05105716319074666</v>
       </c>
       <c r="W95">
-        <v>0.2236312663058544</v>
+        <v>0.223760720919622</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1720205498182862</v>
+        <v>0.1701905439691555</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2424354038363143</v>
+        <v>0.2443354038363144</v>
       </c>
       <c r="C96">
-        <v>-911.350226728645</v>
+        <v>-925.5529705612075</v>
       </c>
       <c r="D96">
-        <v>183.043773271355</v>
+        <v>181.2920294387925</v>
       </c>
       <c r="E96">
-        <v>1119.294</v>
+        <v>1131.745</v>
       </c>
       <c r="F96">
-        <v>1170.394</v>
+        <v>1182.845</v>
       </c>
       <c r="G96">
         <v>76</v>
@@ -9159,37 +9159,37 @@
         <v>46.969</v>
       </c>
       <c r="M96">
-        <v>275.9789052</v>
+        <v>278.914851</v>
       </c>
       <c r="N96">
-        <v>-229.0099052</v>
+        <v>-231.945851</v>
       </c>
       <c r="O96">
-        <v>-68.70297155999999</v>
+        <v>-69.58375529999999</v>
       </c>
       <c r="P96">
-        <v>-160.30693364</v>
+        <v>-162.3620957</v>
       </c>
       <c r="Q96">
-        <v>-159.37593364</v>
+        <v>-161.4310957</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.535005436197829</v>
+        <v>0.632846523437395</v>
       </c>
       <c r="T96">
-        <v>6.734096968626918</v>
+        <v>8.080916362352305</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.05105716319074666</v>
+        <v>0.05051971936768616</v>
       </c>
       <c r="W96">
-        <v>0.223760720919622</v>
+        <v>0.2238874501730996</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1701905439691555</v>
+        <v>0.1683990645589538</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2443354038363144</v>
+        <v>0.2462354038363143</v>
       </c>
       <c r="C97">
-        <v>-925.5529705612075</v>
+        <v>-939.7225035615703</v>
       </c>
       <c r="D97">
-        <v>181.2920294387925</v>
+        <v>179.5734964384298</v>
       </c>
       <c r="E97">
-        <v>1131.745</v>
+        <v>1144.196</v>
       </c>
       <c r="F97">
-        <v>1182.845</v>
+        <v>1195.296</v>
       </c>
       <c r="G97">
         <v>76</v>
@@ -9241,37 +9241,37 @@
         <v>46.969</v>
       </c>
       <c r="M97">
-        <v>278.914851</v>
+        <v>281.8507968</v>
       </c>
       <c r="N97">
-        <v>-231.945851</v>
+        <v>-234.8817968</v>
       </c>
       <c r="O97">
-        <v>-69.58375529999999</v>
+        <v>-70.46453904000001</v>
       </c>
       <c r="P97">
-        <v>-162.3620957</v>
+        <v>-164.41725776</v>
       </c>
       <c r="Q97">
-        <v>-161.4310957</v>
+        <v>-163.48625776</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.632846523437395</v>
+        <v>0.779608154296744</v>
       </c>
       <c r="T97">
-        <v>8.080916362352305</v>
+        <v>10.10114545294038</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.05051971936768616</v>
+        <v>0.04999347229093943</v>
       </c>
       <c r="W97">
-        <v>0.2238874501730996</v>
+        <v>0.2240115392337965</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1683990645589538</v>
+        <v>0.1666449076364648</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2462354038363143</v>
+        <v>0.2481354038363143</v>
       </c>
       <c r="C98">
-        <v>-939.7225035615697</v>
+        <v>-953.8597613136193</v>
       </c>
       <c r="D98">
-        <v>179.57349643843</v>
+        <v>177.8872386863806</v>
       </c>
       <c r="E98">
-        <v>1144.196</v>
+        <v>1156.647</v>
       </c>
       <c r="F98">
-        <v>1195.296</v>
+        <v>1207.747</v>
       </c>
       <c r="G98">
         <v>76</v>
@@ -9323,37 +9323,37 @@
         <v>46.969</v>
       </c>
       <c r="M98">
-        <v>281.8507968</v>
+        <v>284.7867426</v>
       </c>
       <c r="N98">
-        <v>-234.8817968</v>
+        <v>-237.8177426</v>
       </c>
       <c r="O98">
-        <v>-70.46453903999999</v>
+        <v>-71.34532277999999</v>
       </c>
       <c r="P98">
-        <v>-164.41725776</v>
+        <v>-166.47241982</v>
       </c>
       <c r="Q98">
-        <v>-163.48625776</v>
+        <v>-165.54141982</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.779608154296742</v>
+        <v>1.024210872395656</v>
       </c>
       <c r="T98">
-        <v>10.10114545294036</v>
+        <v>13.46819393725381</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.04999347229093944</v>
+        <v>0.04947807566938336</v>
       </c>
       <c r="W98">
-        <v>0.2240115392337965</v>
+        <v>0.2241330697571594</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1666449076364648</v>
+        <v>0.1649269188979445</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2481354038363143</v>
+        <v>0.2500354038363143</v>
       </c>
       <c r="C99">
-        <v>-953.8597613136193</v>
+        <v>-967.9656445863304</v>
       </c>
       <c r="D99">
-        <v>177.8872386863806</v>
+        <v>176.2323554136695</v>
       </c>
       <c r="E99">
-        <v>1156.647</v>
+        <v>1169.098</v>
       </c>
       <c r="F99">
-        <v>1207.747</v>
+        <v>1220.198</v>
       </c>
       <c r="G99">
         <v>76</v>
@@ -9405,37 +9405,37 @@
         <v>46.969</v>
       </c>
       <c r="M99">
-        <v>284.7867426</v>
+        <v>287.7226884</v>
       </c>
       <c r="N99">
-        <v>-237.8177426</v>
+        <v>-240.7536884</v>
       </c>
       <c r="O99">
-        <v>-71.34532277999999</v>
+        <v>-72.22610651999999</v>
       </c>
       <c r="P99">
-        <v>-166.47241982</v>
+        <v>-168.52758188</v>
       </c>
       <c r="Q99">
-        <v>-165.54141982</v>
+        <v>-167.59658188</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.024210872395656</v>
+        <v>1.513416308593484</v>
       </c>
       <c r="T99">
-        <v>13.46819393725381</v>
+        <v>20.20229090588072</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.04947807566938336</v>
+        <v>0.04897319734622638</v>
       </c>
       <c r="W99">
-        <v>0.2241330697571594</v>
+        <v>0.2242521200657598</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1649269188979445</v>
+        <v>0.1632439911540879</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2500354038363143</v>
+        <v>0.2519354038363144</v>
       </c>
       <c r="C100">
-        <v>-967.9656445863304</v>
+        <v>-982.0410209382543</v>
       </c>
       <c r="D100">
-        <v>176.2323554136695</v>
+        <v>174.6079790617456</v>
       </c>
       <c r="E100">
-        <v>1169.098</v>
+        <v>1181.549</v>
       </c>
       <c r="F100">
-        <v>1220.198</v>
+        <v>1232.649</v>
       </c>
       <c r="G100">
         <v>76</v>
@@ -9487,37 +9487,37 @@
         <v>46.969</v>
       </c>
       <c r="M100">
-        <v>287.7226884</v>
+        <v>290.6586342</v>
       </c>
       <c r="N100">
-        <v>-240.7536884</v>
+        <v>-243.6896342</v>
       </c>
       <c r="O100">
-        <v>-72.22610651999999</v>
+        <v>-73.10689026</v>
       </c>
       <c r="P100">
-        <v>-168.52758188</v>
+        <v>-170.58274394</v>
       </c>
       <c r="Q100">
-        <v>-167.59658188</v>
+        <v>-169.65174394</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.513416308593484</v>
+        <v>2.981032617186968</v>
       </c>
       <c r="T100">
-        <v>20.20229090588072</v>
+        <v>40.40458181176143</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.04897319734622638</v>
+        <v>0.04847851858515339</v>
       </c>
       <c r="W100">
-        <v>0.2242521200657598</v>
+        <v>0.2243687653176208</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1632439911540879</v>
+        <v>0.1615950619505113</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2519354038363144</v>
-      </c>
-      <c r="C101">
-        <v>-982.0410209382543</v>
-      </c>
-      <c r="D101">
-        <v>174.6079790617456</v>
-      </c>
-      <c r="E101">
-        <v>1181.549</v>
-      </c>
-      <c r="F101">
-        <v>1232.649</v>
-      </c>
-      <c r="G101">
-        <v>76</v>
-      </c>
-      <c r="H101">
-        <v>1194</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>47.9</v>
-      </c>
-      <c r="K101">
-        <v>0.931</v>
-      </c>
-      <c r="L101">
-        <v>46.969</v>
-      </c>
-      <c r="M101">
-        <v>290.6586342</v>
-      </c>
-      <c r="N101">
-        <v>-243.6896342</v>
-      </c>
-      <c r="O101">
-        <v>-73.10689026</v>
-      </c>
-      <c r="P101">
-        <v>-170.58274394</v>
-      </c>
-      <c r="Q101">
-        <v>-169.65174394</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.981032617186968</v>
-      </c>
-      <c r="T101">
-        <v>40.40458181176143</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.04847851858515339</v>
-      </c>
-      <c r="W101">
-        <v>0.2243687653176208</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1615950619505113</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
